--- a/UK_100_companies.xlsx
+++ b/UK_100_companies.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Топ для старта (A)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'100 компаний'!$A$1:$Q$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'100 компаний'!$A$1:$R$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -471,15 +471,16 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="44" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
-    <col width="50" customWidth="1" min="17" max="17"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,45 +526,50 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Что предложить</t>
+          <t>Предложение 1 (быстрый результат)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Предложение 2 (продукт посерьёзнее)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Ниши</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Приоритет для новичка</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Кому писать (ЛПР)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Публичные email (найдены в источниках)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Шаблон корп. email / гипотеза адреса ЛПР (НЕ проверено)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Телефон / адрес</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Важно / проверить</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
@@ -610,45 +616,50 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Аудит и починка чекаута/платежей + AI-бот статуса заказа и предзаказа (автописьма о сроках, перенос/отмена в 1 клик).</t>
+          <t>Аудит и починка оплаты на hornby.com: найти, где и почему банк отклоняет карты, добавить Apple Pay и Google Pay, настроить алерты о сбоях оплаты. Результат: меньше брошенных корзин и жалоб «сайт не принимает оплату».</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>Трекер предзаказов: личная страница с ожидаемой датой, автописьма при переносе, кнопки «ждать», «заменить» или «вернуть деньги». Результат: предзаказы перестают отменяться молча через несколько месяцев.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
           <t>N1, N3</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>CEO Olly (Oliver) Raeburn; PR: Holly Barnett</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>— (в RNS email не указан)</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
           <t>01843 233 500</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>В 2026 продана Scalextric (сделка с Castelnau) — компания перестраивается, хороший момент для предложений.</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/hornby.com</t>
         </is>
@@ -695,41 +706,46 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Хелпдеск с AI-триажем писем + страница «где мой заказ» + автосообщения о задержках.</t>
+          <t>AI-триаж почты поддержки: входящие письма сортируются по темам (доставка, брак, возврат, подарочная карта), получают приоритет и готовый черновик ответа. Результат: ответ за часы, а не за дни.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
+          <t>Страница «Где мой заказ» с данными курьера и автоматическими письмами о задержке, плюс самостоятельная проверка баланса подарочной карты. Результат: меньше звонков и писем со статусом заказа.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
           <t>N1, N2</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>CEO Steven Crowe; CFO Sam Copeman</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>anglingdirect@fticonsulting.com (IR-агентство FTI)</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
           <t>+44 1603 258 658</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>https://resolver.co.uk/companies/angling-direct-complaints ; https://www.reviews.io/company-reviews/store/anglingdirect/4p</t>
         </is>
@@ -776,45 +792,50 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Портал возвратов с фото-приёмкой + AI-ответы на письма с SLA + сбор отзывов после покупки.</t>
+          <t>Портал возвратов и брака: клиент загружает фото, система сразу решает по правилам (обмен, возврат или ваучер) и показывает статус. Результат: меньше споров и негативных отзывов про отказы.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>Контроль обещания «ответ за 48 часов»: таймер на каждое письмо, эскалация при просрочке и AI-черновики ответов. Плюс автоматическая просьба оставить отзыв после покупки, чтобы поднять рейтинг reviews.io (сейчас 2.2).</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>N1, N2</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>CEO Anthony Smith (по RNS 2021 — проверить)</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>— (в RNS скрыт)</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>по данным Prospeo: first.last@shoezone.net (не проверено)</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>+44 116 222 3000; Haramead Business Centre, Leicester LE1 2LH</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Уточнить актуального CEO.</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/shoezone.ie ; https://www.reviews.io/company-reviews/store/www-shoezone-com</t>
         </is>
@@ -861,41 +882,46 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Трекинг-страница + проактивные уведомления о задержках + AI-бот поддержки; модуль ответов на отзывы.</t>
+          <t>Проактивные уведомления о задержках: если посылка Evri застряла дольше X дней, клиент сам получает письмо или SMS с новым сроком и кнопкой «вернуть деньги». Результат: меньше заказов, которые «не пришли», и меньше злых отзывов.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>AI-ассистент поддержки на сайте и в почте плюс модуль ответов на отзывы в Trustpilot (сейчас компания не отвечает на негатив). Результат: рейтинг 2.0 начинает расти, обращения закрываются быстрее.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>N1, N2</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>CEO Gavin Peck</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>— (в RNS скрыт)</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>по данным LeadIQ: First.Last@theworks.co.uk → gavin.peck@theworks.co.uk (не проверено)</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>+44 121 313 6050; Boldmere House, Hams Hall, Coleshill</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/www.theworks.co.uk?page=2</t>
         </is>
@@ -942,45 +968,50 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>D2C-витрина/лендинги брендов + система сбора отзывов и ответа на них + AI-поддержка.</t>
+          <t>Программа сбора отзывов для брендов W7 и Technic: QR-код на упаковке ведёт на форму отзыва и в соцсети. Результат: сотни настоящих отзывов вместо 26 и 3.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>Лендинги и D2C-витрина для бестселлеров с интеграцией в Amazon и ритейлеров, плюс AI-ответы на вопросы о составе продуктов. Результат: собственный канал продаж и данные о покупателях.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>N2, N3</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>CEO Sam Bazini; MD Eoin Macleod</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>florence.chandler@investor-focus.co.uk (IR-агентство IFC, 2024 — проверить)</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
           <t>+44 1753 639130 (Iver)</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>Компания растёт сделками (Brand Architekts, 2026).</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>https://ca.trustpilot.com/review/w7makeup.co.uk</t>
         </is>
@@ -1027,45 +1058,50 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Мониторинг жалоб с авто-классификацией + бот статуса заказа (сайт + WhatsApp).</t>
+          <t>Бот статуса заказа в WhatsApp и на сайте: показывает, где посылка, и сам оформляет рефанд, если заказ не ушёл со склада за N дней. Результат: меньше случаев «деньги списали, а заказ не отправили».</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>Дашборд жалоб: AI сводит в одну картину Resolver, Trustpilot и письма, отделяя качество продукта от сервиса, и каждую неделю отправляет отчёт продуктовой команде. Результат: видно, какой продукт и какой процесс ломаются.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>N1, N2</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>CEO Tom Allsworth; CFO Neil Catto</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Investor.Relations@revolutionbeautyplc.com (IR); help@revolutionbeauty.com (поддержка)</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>Great Pulteney St, London W1F 9NB</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>Расследование FCA прекращено (06/2026).</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>https://resolver.co.uk/companies/revolution-beauty-complaints ; https://ie.trustpilot.com/review/revolutionbeauty.com</t>
         </is>
@@ -1112,41 +1148,46 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Портал возвратов + автоматический статус рефанда; проверка цен/промо на сайте скриптом.</t>
+          <t>Портал возвратов с онлайн-статусом рефанда, особенно для международных заказов. Результат: меньше писем «где мои деньги» и меньше жалоб на задержки.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>Скрипт ежедневной проверки цен и промо на сайте: сверяет, что цена в карточке, в корзине и в акции совпадает, и шлёт алерт при расхождении. Результат: уходит жалоба «на сайте одна цена, а списали другую».</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>N1, N3</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Joint CEOs Julie Lavington и Ali Hall; CFO Steve Dilks</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>sosandar@almastrategic.com (PR-агентство Alma)</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>IR: sosandar-ir.com</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>https://ie.trustpilot.com/review/www.sosandar.com</t>
         </is>
@@ -1193,41 +1234,46 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Проактивные уведомления о задержках по 10+ странам + аналитика причин негатива (VoC-дашборд).</t>
+          <t>Мониторинг доставок по всем странам: обнаружение «застрявших» посылок и автоматические письма клиенту раньше, чем он начнёт жаловаться. Результат: меньше негатива про пропавшие заказы.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>Дашборд причин негатива (Voice of Customer): AI разбирает 140k отзывов и показывает, что именно портит оценку и в каких странах. Плюс персонализация шаблонных ответов поддержки, на которые жалуются.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>N1, N2</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>CEO Gareth Bevan; Exec Chair Andrew Wass (основатель); CFO Chris Scott</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>info@gear4music.com (общий)</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>first.last@gear4music.com (Prospeo, 54%) → gareth.bevan@gear4music.com (не проверено)</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>https://au.trustpilot.com/review/www.gear4music.com</t>
         </is>
@@ -1274,41 +1320,46 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Мониторинг ошибок оформления заказа + автописьма при сбое оплаты/заказа + бот статуса.</t>
+          <t>Мониторинг сбоев оформления заказа: если заказ упал с технической ошибкой, клиент сразу получает письмо и ссылку на повтор, а команда — алерт. Результат: исчезают жалобы «ошибка, и никто не сказал».</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>Self-service «открытка не пришла»: клиент нажимает кнопку, система проверяет трекинг и предлагает перепечатать открытку или выдать ваучер. Плюс напоминание взять письмо-подтверждение для выдачи шаров в магазине.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>N1, N3</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>CEO Darcy Willson-Rymer; CFO Matthias Seeger</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>— (IR через Teneo; страница cardfactoryinvestors.com/contacts)</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>Century House, Brunel Road, Wakefield WF2 0XG</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>https://de.trustpilot.com/review/www.cardfactory.co.uk</t>
         </is>
@@ -1355,34 +1406,34 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Self-service компенсаций за опоздавшую доставку (правила + авто-рефанд) + бот поддержки для IE.</t>
+          <t>Автоматическая компенсация за опоздание next-day доставки: если трекинг подтверждает опоздание, деньги за доставку возвращаются без обращения. Результат: меньше 1★ отзывов и меньше нагрузки на поддержку.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
+          <t>AI-бот поддержки и понятная страница контактов для moonpig.ie (там рейтинг 1.5): рабочий канал жалоб вместо «отключённого» номера телефона.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>N1, N2</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>CEO Catherine Faiers (с 03/2026); CFO Andy MacKinnon</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>investors@moonpig.com (IR); moonpig@client.sodali.com (медиа); trustpilot@moonpig.com (поддержка)</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -1390,10 +1441,15 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
           <t>Новый CEO = окно для новых проектов.</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>https://au.trustpilot.com/review/moonpig.ie ; https://uk.trustpilot.com/review/moonpig.com?page=8</t>
         </is>
@@ -1440,41 +1496,46 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Прозрачный кабинет подписки: отмена/пауза в 2 клика, напоминания о списании (под требования DMCC Act).</t>
+          <t>Кабинет подписки Angel: отмена, пауза и изменение суммы в 2 клика, напоминание перед каждым списанием, честный экран удержания без dark patterns. Готовность к требованиям DMCC Act о подписках.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>Автоматический возврат остатка баланса и удаление аккаунта по кнопке. Плюс мониторинг «списаний после отмены» с алертом. Результат: уходит главная причина негативных отзывов.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>N6, N1</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>CEO Rodrigo Maza; CFO Dominic Neary; IR Catherine Miles</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>IR@nakedwines.com</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>https://nl-be.trustpilot.com/review/nakedwines.co.uk</t>
         </is>
@@ -1521,45 +1582,50 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Кабинет клуба с прозрачными условиями + база знаний и полномочия для агентов (бот с правилами компенсаций).</t>
+          <t>Внутренний бот с правилами компенсаций для агентов: какую скидку, возврат или замену можно дать сразу, без эскалации. Результат: поддержка снова «может решать проблемы».</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>Страница условий клуба простым языком плюс калькулятор «что я получу и что заплачу». Результат: меньше ощущения «мелкого шрифта» и обвинений в нечестности.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>N6, N1</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>CEO Jay Wright; CFO Amanda Cherry</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>— (через PR Hudson Sandler)</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>virginwinesplc.co.uk</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>Доказательства слабее среднего.</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>https://ie.trustpilot.com/review/www.virginwines.co.uk</t>
         </is>
@@ -1606,41 +1672,46 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Единый трекер обращений (магазин+офис) + статус рефанда для клиента + AI-ответы на отзывы.</t>
+          <t>Единый трекер обращений для магазина, колл-центра и офиса: у клиента один номер обращения и онлайн-статус, клиента больше не перекидывают между отделами.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>Автоматический статус рефанда за возвраты и сэмплы плюс AI-черновики ответов на отзывы. Результат: отвечать на 100% негатива в течение суток вместо 64% за неделю.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>N1, N2</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>CEO Alex Jensen (назначен на смену Rob Parker — проверить); Co Sec Joanne Steer</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Joanne.steer@toppstiles.co.uk (Co Sec); toppstiles@citigatedewerogerson.com (IR-агентство)</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>first.last@toppstiles.co.uk (из опубл. адреса) → alex.jensen@toppstiles.co.uk (не проверено)</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>+44 116 282 8000</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/toppstiles.co.uk</t>
         </is>
@@ -1687,41 +1758,46 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Аудит и фиксы онлайн-записи (MOT/шины): синхронизация слотов, письма-подтверждения, статус в SMS.</t>
+          <t>Аудит и фиксы онлайн-записи в автосервис: слоты MOT синхронизируются с реальным графиком, оплата списывается только после подтверждения, письмо и SMS подтверждают запись.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
+          <t>Модуль ответов на отзывы Autocentres (135k отзывов, на негатив не отвечают) с AI-черновиками и маршрутизацией жалобы в конкретный сервис-центр.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>N3, N2</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>CEO Henry Birch; Dir Corporate Affairs &amp; IR Holly Cassell</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>investor.relations@halfords.co.uk (IR); halfords@teneo.com (медиа)</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/www.halfords.com/mot ; https://www.reviews.io/company-reviews/store/halfords-autocentres/EJ</t>
         </is>
@@ -1768,41 +1844,46 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Портал доставки (точное окно, перенос, фото-подтверждение) + AI-триаж претензий по качеству с фото.</t>
+          <t>Портал доставки: точное окно доставки, перенос в 1 клик, фото-подтверждение от бригады, честный статус «почему не доставили». Результат: меньше «failed delivery» неделями.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>AI-триаж претензий по качеству: клиент загружает фото дефекта, система классифицирует его (брак или износ), сразу записывает техника и ведёт статус.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>N1, N3</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>CEO Tim Stacey (проверить 2026); IR Phil Hutchinson</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>investor.relations@dfs.co.uk</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>1 Rockingham Way, Doncaster DN6 7NA</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>https://ca.trustpilot.com/review/dfs.ie</t>
         </is>
@@ -1849,41 +1930,46 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Трекер проектов установки (этапы, фото, ответственные, SLA) для клиента и офиса.</t>
+          <t>Трекер проекта установки кухни или ванной: этапы, даты, ответственный монтажник, фото работ. Клиент видит прогресс без звонков.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
+          <t>Контроль обещаний: когда менеджер обещает компенсацию или перезвон, они фиксируются в системе с дедлайном и автоматическим напоминанием. Результат: уходят жалобы «пообещали и не сделали».</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>N5, N1</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>CEO David Wood; CFO Mark George; IR Holly Grainger</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>investorrelations@wickes.co.uk (IR); wickes@headlandconsultancy.com (медиа)</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/www.wickes.co.uk/location/chadwell-heath</t>
         </is>
@@ -1930,41 +2016,46 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Хелпдеск с SLA и AI-черновиками ответов + честный сбор отзывов после покупки.</t>
+          <t>Хелпдеск с SLA: у каждого письма таймер, AI-черновик и эскалация. Шаблонные ответы «передали в отдел» заменяются реальным решением.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>Честная программа отзывов: автоматическая просьба об отзыве после доставки и отдельный путь для решения проблемы до публикации. Результат: reviews.io 1.7 начинает расти.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>N1, N2</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>CEO Lee Tappenden; CFO Dan Walden</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>investor.relations@procook.co.uk (IR); procook@mhpgroup.com (PR)</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>procookgroup.co.uk</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>https://www.reviews.io/company-reviews/store/procook</t>
         </is>
@@ -2011,45 +2102,50 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Фото-подтверждение доставки и установки + бот разбора претензий.</t>
+          <t>Фото-подтверждение доставки и установки в приложении водителя (геометка, время, подпись клиента). Результат: уходят споры «доставлено, а на самом деле нет».</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>Бот приёма претензий после доставки: что входило в заказ (установка, вывоз старой техники), что было сделано, автоматическое решение. Результат: меньше путаницы между водителем и офисом.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>N1, N7</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>CEO Mark Smithson (основатель; проверить)</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>complaints@markselectrical.co.uk (жалобы)</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>4 Boston Road, Leicester LE4 1AU</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>Доказательства слабее среднего.</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>https://www.feefo.com/en-GB/reviews/marks-electrical?page=4</t>
         </is>
@@ -2096,34 +2192,34 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Портал повреждений/возвратов с фото при доставке и авто-решением (замена/рефанд по правилам).</t>
+          <t>Фото-приёмка повреждений при доставке: клиент снимает товар в течение 48 часов, система сразу оформляет замену или рефанд. Результат: меньше недель переписки.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>Трекер возвратов: клиент видит, когда товар принят на складе и когда придут деньги, а склад обязан фотографировать возврат при приёмке, чтобы не спорить о том, кто его повредил.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>N1, N7</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>CEO Stephnie Judge (с 04/2026); CFO Daniel Barton</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>VictorianPlumbing@fticonsulting.com (IR-агентство)</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -2131,10 +2227,15 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
           <t>Новый CEO.</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>https://nz.trustpilot.com/review/www.victorianplumbing.co.uk ; https://www.reviews.co.uk/company-reviews/store/victorian-plumbing/Qr</t>
         </is>
@@ -2181,29 +2282,29 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Единый портал возвратов для маркетплейса + прозрачная маркировка продавца + эскалация на человека.</t>
+          <t>Единый портал возвратов для маркетплейса: один вход для товаров Debenhams и сторонних продавцов, общий статус рефанда, понятно, кто продавец и кто возвращает деньги.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
+          <t>Кнопка «живой человек» в боте: распознавание зацикливания и эскалация на агента после 2 неудачных ответов. Результат: меньше обращений в Trading Standards и FOS.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
           <t>N1, N3</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>CEO Dan Finley (по данным 2025 — проверить)</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -2211,15 +2312,20 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
           <t>+44 161 233 2050</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>Крупная структура — сложнее зайти.</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>https://nz.trustpilot.com/review/www.boohoo.com?page=4 ; https://ground.news/article/delays-to-debenhams-refunds-study-finds-50-of-consumers-wont-shop-again-after-slow-refunds-internetretailing</t>
         </is>
@@ -2266,34 +2372,34 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Автоматизация рефандов и проверок «срок годности/неверный товар» по фото + статус в ЛК.</t>
+          <t>Автоматизация рефандов по фото: клиент загружает снимок неверного товара или срока годности, AI проверяет его и сразу оформляет возврат. Результат: рефанд за дни вместо 2 месяцев.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>Мониторинг трекинга: детектор «не обновляется больше 3 дней» с проактивным письмом клиенту. Плюс контроль сроков годности на складе перед отправкой.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>N1, N2</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>CEO Matthew Moulding; IR Kate Grimoldby</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>Investor.relations@thg.com (IR); media-enquiries@thg.com (медиа)</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -2301,10 +2407,15 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>Своя большая IT-команда — заходить через узкий пилот.</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/myprotein.ie</t>
         </is>
@@ -2351,45 +2462,50 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Лёгкий хелпдеск для онлайн-магазина + форма «бой/брак» с фото + проверка правил доставки в корзине.</t>
+          <t>Онлайн-форма «бой или брак» с фото и номером заказа, которая сразу отправляет в работу правильную замену (того же сервиза). Результат: заменяют то, что нужно, а не что-то другое.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
+          <t>Проверка правил доставки в корзине (бесплатная доставка выше порога) и единый канал поддержки онлайн-заказов вместо «по телефону онлайн-заказами не занимаемся».</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>N1, N3</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Group CEO Michael Scheepers (06/2026); FD Jonathan Hill</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>PortmeirionGroup@houston.co.uk (PR-агентство Houston)</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>London Road, Stoke-on-Trent ST4 7QQ</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>Новый CEO.</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>https://de.trustpilot.com/review/www.portmeirion.co.uk ; https://www.reviews.co.uk/company-reviews/store/portmeirion-group-limited</t>
         </is>
@@ -2436,41 +2552,46 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-портал ремонта: заявка с фото, смета до отправки, статус и сроки; премиальный пост-покупочный сервис.</t>
+          <t>Онлайн-портал ремонта: заявка с фото, предварительная смета до отправки сумки, статус и срок ремонта. Результат: прозрачность вместо сюрприза «ремень за £240».</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
+          <t>Премиальный пост-покупочный сервис: проверка подарочной записки и упаковки перед отправкой, персональный менеджер для повторных клиентов. Результат: защита люксового бренда в отзывах.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>N7, N1</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>CEO Andrea Baldo (проверить: смена директоров 08/2026)</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>companysecretary@mulberry.com; mulberry@headlandconsultancy.com (PR)</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
           <t>+44 20 7605 6793</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>https://nz.trustpilot.com/review/www.mulberry.com ; https://uk.trustpilot.com/review/mulberry.co.uk</t>
         </is>
@@ -2517,45 +2638,50 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Регистрация гарантии через QR на коробке за 30 секунд + онлайн-претензия с фото.</t>
+          <t>Регистрация гарантии через QR на коробке за 30 секунд, с напоминанием «зарегистрируйте до 30 дня». Результат: меньше отказов по гарантии и больше данных о покупателях.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>Онлайн-претензия по гарантии с фото и видео, автоматическим решением и прямой доставкой замены, без отправки клиента обратно в магазин. Результат: меньше негатива к брендам Salter и Beldray.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>N7, N1</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>Новый CEO Simon Harrison (с 26.10.2026; Andrew Gossage ушёл)</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>— (вопросы через investors.upplc.com)</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t>+44 161 627 1400</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>Только что сменился CEO — идеальное окно.</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>https://trustpilot.com/review/upplc.com ; https://www.reviews.io/company-reviews/store/salterhousewares</t>
         </is>
@@ -2602,45 +2728,50 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-визуализатор/примерка обоев + отдельный модуль заказа и трекинга сэмплов.</t>
+          <t>Онлайн-визуализатор: клиент загружает фото комнаты и примеряет обои или ткань Morris &amp; Co. Результат: меньше ошибок с цветом и больше продаж.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>Отдельный модуль заказа сэмплов с трекингом каждого образца и понятной маркировкой, кто продавец (Morris &amp; Co или партнёр). Результат: уходят жалобы «оплатил 10 сэмплов, пришло 2».</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>N7, N3</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>CEO Lisa Montague; CFO Mike Woodcock</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>SDG@buchanan.uk.com (PR, 2024 — проверить)</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>PR: Burson Buchanan +44 20 7466 5000</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>10/2026 активист-акционер добивается смены председателя.</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/wmorrisandco.com ; https://www.reviews.io/company-reviews/store/wmorrisandco.com/insights</t>
         </is>
@@ -2687,41 +2818,46 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Подтверждение надписи клиентом (превью) + единый трекер жалоб по 230+ франшизам с SLA.</t>
+          <t>Превью надписи на торте: клиент подтверждает текст и картинку перед изготовлением, а франшиза видит утверждённый макет. Результат: меньше ошибок в именах.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
+          <t>Центральный трекер жалоб для 230+ франшиз: SLA, статистика по магазинам, автоматическое решение (переделка или компенсация). Результат: проблемы не теряются на уровне отдельной точки.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
           <t>N1, N7</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>CEO Sukh Chamdal (основатель; по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>— (не найден в рамках лимита поиска)</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
           <t>cakebox.com</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="2" t="inlineStr">
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>https://ca.trustpilot.com/review/cakebox.com?page=5</t>
         </is>
@@ -2768,45 +2904,50 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>PWA вместо отсутствующего Android-приложения + починка учёта членства и подарочных карт.</t>
+          <t>PWA (веб-приложение, которое ставится на телефон) для Android-пользователей и членов клуба: членские билеты, бронирование и подарочные карты без нативного приложения.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
+          <t>Починка учёта членства: корректная дата продления, баланс билетов, одинаковые комиссии в приложении и на сайте, приём e-подарочных карт онлайн. Результат: уходят главные жалобы с Trustpilot (2.5).</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>N3, N6</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Interim CEO Farah Golant CBE (02/2026); FD Will Worsdell</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>everyman@almastrategic.com (PR, старый — проверить)</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
           <t>020 3145 0500</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>Смена руководства.</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/www.everymancinema.com</t>
         </is>
@@ -2853,29 +2994,29 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-бронирование с апсейлами, депозитами и автонапоминаниями + CRM повторных визитов.</t>
+          <t>Новая воронка онлайн-бронирования: пакеты для групп, депозиты, апсейлы (еда, напитки, доп. игры), автонапоминания и снижение неявок. Результат: выручка с той же посещаемости.</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
+          <t>CRM повторных визитов: сбор контактов, акции на дни рождения и корпоративы, сегменты для рассылок. Результат: больше повторных посещений на слабом рынке.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
           <t>N3, N6</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>CEO Richard Harpham</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -2883,15 +3024,20 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t>+44 20 7846 3322</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>Компании нужна выручка — продавать через рост конверсии.</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>https://www.morningadvertiser.co.uk/Article/2026/09/07/xp-factory-hit-by-weaker-competitive-socialising-market/ ; https://nl-be.trustpilot.com/review/boombattlebar.com?page=2</t>
         </is>
@@ -2938,41 +3084,46 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Мобильная версия бронирования/QR-заказа + система ответа на отзывы и жалобы.</t>
+          <t>Мобильная версия бронирования и QR-заказа: работает на любом телефоне и не запрашивает повторно данные, уже введённые для Wi-Fi.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
+          <t>Система приёма жалоб и ответов на отзывы по всем пабам: каждая жалоба уходит менеджеру паба с дедлайном. Результат: перестают теряться жалобы «3 раза писал — нет ответа».</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
           <t>N3, N2</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>CEO Justin Platt; Dir Corporate Affairs Giles Robinson</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>matthew.lee@marstons.co.uk (IR, 2025)</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>first.last@marstons.co.uk (из опубл. адреса) → justin.platt@marstons.co.uk (не проверено)</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>01902 907250</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/marstons.co.uk?page=4</t>
         </is>
@@ -3019,45 +3170,50 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Аудит UX app: геолокация, очередь заказов app vs бар (KDS-приоритизация), ETA для гостя.</t>
+          <t>UX-аудит приложения: правильный «ближайший паб» по геолокации, сохранение корзины при оплате, понятный статус заказа для гостя.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
+          <t>Время ожидания заказа в приложении: прогноз для гостя и приоритизация заказов из app на экране бара наравне с заказами у стойки.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>CEO John Hutson; Chairman Tim Martin</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>investorqueries@jdwetherspoon.co.uk</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
           <t>01923 477777; Wetherspoon House, Watford WD24 4QL</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>Консервативная компания, своё приложение.</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>https://ca.trustpilot.com/review/www.jdwetherspoon.com?page=7 ; https://www.thecaterer.com/news/wetherspoon-boss-defends-app-amid-qr-code-backlash</t>
         </is>
@@ -3104,45 +3260,50 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Автоматический детектор двойных списаний и мгновенный рефанд + QA-аудит чекаута app.</t>
+          <t>Детектор двойных списаний: ежедневная сверка платежей и заказов с автоматическим рефандом без участия франчайзи. Результат: уходят конфликты «магазин отказал в возврате».</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
+          <t>QA-аудит чекаута в приложении: зависания на оплате, сообщения об ошибках, кастомизация безглютеновой пиццы, с отчётом и приоритетами исправлений.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
           <t>N3, N1</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>CEO Nicola Frampton (с 03/2026); Dir IR Michael Barker</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>— (IR по телефону +44 7345 418580; PR Brunswick)</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
           <t>+44 7345 418580</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>Франчайзинговая модель — уточнять, кто владеет app.</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>https://ie.trustpilot.com/review/www.dominos.co.uk</t>
         </is>
@@ -3189,41 +3350,46 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Синхронизация онлайн-брони с залом + единая система ответов на жалобы по брендам.</t>
+          <t>Синхронизация онлайн-брони с планом зала: персонал видит бронь, гость получает подтверждение со столом. Результат: «вашей брони нет» больше не случается.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
+          <t>Единая система ответа на письма и отзывы по брендам Toby, Harvester и All Bar One: AI-черновики, назначение ответственного, SLA.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
           <t>N2, N3</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>CEO Phil Urban (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>— (не найден в рамках лимита поиска)</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
           <t>mbplc.com</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr"/>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/mbplc.com ; https://ch.trustpilot.com/review/www.toby.co.uk</t>
         </is>
@@ -3270,29 +3436,29 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Сбор отзывов после визита/брони + мониторинг и ответы (Google + Trustpilot + TripAdvisor).</t>
+          <t>Автоматический сбор отзывов после брони или визита (Google, Trustpilot, TripAdvisor). Результат: вместо 35 случайных отзывов появляются сотни реальных.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
+          <t>Мониторинг и ответы на отзывы по 380 пабам и отелям с еженедельным отчётом проблем по каждой точке.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>CEO Simon Emeny (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -3300,15 +3466,20 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
           <t>fullers.co.uk</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>Доказательства слабые (мало отзывов) — это и есть аргумент.</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>https://ca.trustpilot.com/review/fullers.co.uk?page=2</t>
         </is>
@@ -3355,45 +3526,50 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Аудит воронки бронирования пакетов + аналитика отказов на шаге оплаты.</t>
+          <t>Аудит воронки бронирования пакетов: почему пропадает доступность пакетов («игра + напиток»), где люди бросают оплату, с отчётом и исправлениями.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
+          <t>Аналитика отзывов и NPS по центрам: какие площадки теряют клиентов и почему, и что исправить в первую очередь.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>CEO Stephen Burns; CFO Antony Smith</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>— (через Headland)</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
           <t>hollywoodbowlgroup.com/investor-relations</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>Доказательства слабые.</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>https://ie.trustpilot.com/users/643eca01faa5920012471fd0</t>
         </is>
@@ -3440,41 +3616,46 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Прозрачная отмена/пауза в app (DMCC) + эскалация с AI на человека + само-разблокировка PIN.</t>
+          <t>Прозрачная отмена и пауза в приложении: доступны в любой день, с понятной датой последнего списания. Готовность к правилам DMCC Act о подписках.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
+          <t>Эскалация с AI-автоответов на человека и самостоятельная разблокировка PIN (подтверждение по SMS). Результат: меньше заблокированных людей у турникета и меньше 1★ отзывов.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
           <t>N6, N1</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>CEO Will Orr; CFO Luke Tait; IR Katharine Wynne</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>reviews@thegymgroup.com (из ответов на Trustpilot)</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
           <t>Team Lewis +44 20 7802 2617; tggplc.com</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="2" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/thegymgroup.com</t>
         </is>
@@ -3521,41 +3702,46 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Личный кабинет продления: сравнение цены, отказ от продления в 1 клик + трекер жалоб.</t>
+          <t>Кабинет продления полиса: сравнение «было и стало» по цене с объяснением роста, отказ от автопродления в 1 клик и подтверждение отказа письмом.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
+          <t>Трекер жалоб для клиентов 50+: простой интерфейс, статус обращения, обратный звонок в выбранный слот вместо ожидания на линии.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
           <t>N6, N4</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>CEO Mike Hazell; IR Emily Roalfe</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>emily.roalfe@saga.co.uk (IR, 09/2026); company.secretary@saga.co.uk</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>first.last@saga.co.uk (из опубл. адреса) → mike.hazell@saga.co.uk (не проверено)</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>3 Pancras Square, London N1C 4AG</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>https://ie.trustpilot.com/review/www.saga.co.uk</t>
         </is>
@@ -3602,45 +3788,50 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Статус рефанда онлайн + эскалация с AI-чата на человека + анти-фишинг страница/верификация писем.</t>
+          <t>Онлайн-статус рефанда: этапы (запрос, авиакомпания, отель, деньги отправлены) и прогноз срока. Результат: меньше писем «5 недель без денег».</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
+          <t>Эскалация с AI-чата на человека при сложных кейсах плюс страница проверки подлинности писем (номер брони и код). Защищает клиентов от фишинга от имени компании.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
           <t>N1, N4</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>CEO Shaun Morton; CSO Adam Hansen (IR/M&amp;A)</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>— (через FTI Consulting +44 20 3727 1000)</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
           <t>Aeroworks, Manchester M1 2NQ</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>Сами признают проблему — сильный повод.</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>https://www.reviews.io/company-reviews/store/onthebeach/7AP ; https://uk.trustpilot.com/review/onthebeach.ie?page=3</t>
         </is>
@@ -3687,41 +3878,46 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>After-sales портал (претензии с фото, статус ремонта) + сверка документов по финансированию.</t>
+          <t>After-sales портал: претензия по неисправности с фото и видео, запись в сервис, статус ремонта. Результат: меньше негатива «после покупки им всё равно».</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
+          <t>Автоматическая сверка документов по автокредиту: цена, admin fee и условия совпадают с тем, что обещал продавец, а расхождения находятся до подписания.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
           <t>N1, N4</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>CEO Mark Carpenter; CFO Chris Morgan</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>— (через FTI Consulting)</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
           <t>motorpoint.co.uk/plc/investor-relations</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr">
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>https://ie.trustpilot.com/review/motorpoint.co.uk/location/manchester</t>
         </is>
@@ -3768,41 +3964,46 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Фото/видео-осмотр при выдаче и сдаче в приложении (таймстемп, разметка, подпись клиента).</t>
+          <t>Приложение фото- и видео-осмотра фургона при выдаче и сдаче: таймстемп, геометка, разметка повреждений, подпись клиента. Результат: меньше споров о плате за повреждения.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
+          <t>Онлайн-оспаривание счёта за повреждения: клиент видит фото «до и после», смету ремонта и может приложить свою смету. Результат: меньше дел в Financial Ombudsman.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
           <t>N7</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>CEO Martin Ward; CFO Philip Vincent; Head IR Ross Hawley</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>— (IR по телефону)</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
           <t>+44 1325 528769; Darlington</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr"/>
-      <c r="Q40" s="2" t="inlineStr">
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>https://www.financial-ombudsman.org.uk/decision/DRN-5596196.pdf</t>
         </is>
@@ -3849,29 +4050,29 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Новый B2B/B2C портал аренды: актуальное наличие, прозрачный калькулятор цены, письмо со сметой.</t>
+          <t>Новый портал аренды: актуальное наличие по депо, калькулятор цены со всеми сборами (доставка, вывоз) и письмо со сметой. Результат: портал перестаёт «падать 99% времени» и скрывать цены.</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
+          <t>Мониторинг заказов: если деньги списаны, а заказ не создан, алерт и автоматический рефанд. Плюс автоматический расчёт дней аренды по фактическим датам доставки и вывоза.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
           <t>N7, N3</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="L41" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>CEO Dan Evans (с 2022 — проверить 2026)</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -3879,15 +4080,20 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
           <t>01942 720 000; Newton-le-Willows</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr">
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>Компания в ответах сама признаёт проблемы с наличием онлайн.</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/speedyhire.com</t>
         </is>
@@ -3934,29 +4140,29 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-регистрация гарантии + запись инженера с точным окном и трекингом.</t>
+          <t>Онлайн-регистрация гарантии Triton через QR, с правильной датой покупки по чеку (фото). Результат: уходят отказы «гарантия истекла» из-за неверной даты.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
+          <t>Запись инженера с точным окном, трекингом «инженер в пути» и честными правилами оплаты визита до записи. Результат: меньше конфликтов из-за £50 и £99.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
           <t>N7, N1</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>CEO Thomas Willcocks; CFO James Eyre</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -3964,11 +4170,16 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
           <t>01625 547700</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr"/>
-      <c r="Q42" s="2" t="inlineStr">
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>https://pl.trustpilot.com/review/tritonshowers.co.uk</t>
         </is>
@@ -4015,45 +4226,50 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Мониторинг комплектности подписочных отправок + авто-уведомления о частичной отгрузке.</t>
+          <t>Контроль комплектности подписочных заказов: сверка «что в подписке — что отгружено» и автоматическое письмо при частичной отправке.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
+          <t>Панель управления подпиской: перенос даты, пауза, смена состава, история отправок. Результат: подписка снова «надёжная».</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
           <t>N6, N1</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>CEO James Bailey (с 03/2026); IR Andrew Porteous</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>— (IR по телефону +44 7740 361849)</t>
         </is>
       </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
           <t>petsathomeplc.com</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>Новый CEO.</t>
         </is>
       </c>
-      <c r="Q43" s="2" t="inlineStr">
+      <c r="R43" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/www.petsathome.com?page=5</t>
         </is>
@@ -4100,34 +4316,34 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-прайс/калькулятор лечения + централизованный учёт жалоб по клиникам.</t>
+          <t>Онлайн-прайс и калькулятор типового лечения по клиникам. Отвечает на требования CMA о прозрачности цен и снижает недоверие клиентов.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
+          <t>Централизованный учёт жалоб 1-й стадии из всех клиник (сейчас они не фиксируются) с аналитикой по клиникам и темам.</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
           <t>N4, N3</t>
         </is>
       </c>
-      <c r="K44" s="4" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>CEO Richard Fairman (уходит на пенсию); IR Charlotte Page</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>cvsg@camarco.co.uk (PR-агентство Camarco)</t>
         </is>
       </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -4135,10 +4351,15 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
           <t>Регуляторный драйвер (CMA) — сильный аргумент.</t>
         </is>
       </c>
-      <c r="Q44" s="2" t="inlineStr">
+      <c r="R44" s="2" t="inlineStr">
         <is>
           <t>https://assets.publishing.service.gov.uk/media/682479c27293a87b6c75ebf8/Summary_of_hearing_with_CVS_.pdf</t>
         </is>
@@ -4185,45 +4406,50 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Портал жалоб: триаж (в т.ч. от claims management), SLA-таймеры FCA, статус для клиента.</t>
+          <t>AI-триаж жалоб: отделяет обращения от claims-компаний и реальных клиентов, классифицирует их и ставит таймеры сроков FCA.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
+          <t>Онлайн-статус жалобы для клиента: что получено, кто рассматривает, когда будет ответ. Результат: меньше повторных обращений и эскалаций в FOS.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
           <t>N4, N2</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>CEO Ian McLaughlin (уходит до конца 2026, interim — John Natalizia); IR James Cranstoun</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>james.cranstoun@vanquis.com (IR)</t>
         </is>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>first.last@vanquis.com (из опубл. адреса)</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
           <t>Регулируемый банк: долгие закупки, нужен партнёр по комплаенсу.</t>
         </is>
       </c>
-      <c r="Q45" s="2" t="inlineStr">
+      <c r="R45" s="2" t="inlineStr">
         <is>
           <t>https://ie.trustpilot.com/review/www.vanquis.co.uk ; https://www.lovemoney.com/news/amp/22331/the-most-complained-about-banks-how-to-complain-win-charges-compensation</t>
         </is>
@@ -4270,41 +4496,46 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>UX-аудит онлайн-банка и онбординга + аналитика багов app по отзывам.</t>
+          <t>UX-аудит онлайн-банка и регистрации: найти, почему люди регистрируются с нескольких попыток и почему их блокирует на 7 дней, и предложить исправления.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
+          <t>AI-аналитика отзывов из App Store и Google Play: классификация багов (Face ID, вход, блокировки) по устройствам и версиям для команды разработки.</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
           <t>N3, N2</t>
         </is>
       </c>
-      <c r="K46" s="4" t="inlineStr">
+      <c r="L46" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>CEO Ian Corfield; IR Phil Deakin</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>ir@securetrustbank.co.uk</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
           <t>0121 693 9100</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr"/>
-      <c r="Q46" s="2" t="inlineStr">
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/securetrustbank.com?page=4</t>
         </is>
@@ -4351,41 +4582,46 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Портал приёма и обработки жалоб/претензий по комиссиям с автоматической классификацией.</t>
+          <t>Портал приёма жалоб и претензий по комиссиям автокредитов: онлайн-форма, проверка данных договора, автоматическая классификация «реальная» или «шаблонная от claims-компании».</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
+          <t>Дашборд жалоб для руководства и FCA: объёмы, сроки, причины, доля закрытых в срок. Результат: проще доказывать регулятору, что процесс под контролем.</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>Chairman/CEO Anthony Coombs</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t>info@suplc.co.uk (общий); sandu@secnewgate.co.uk (PR)</t>
         </is>
       </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
           <t>Solihull</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr"/>
-      <c r="Q47" s="2" t="inlineStr">
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr">
         <is>
           <t>https://www.feefo.com/en-GB/reviews/advantage-finance-ltd ; https://www.nasdaq.com/articles/su-plc-navigates-court-rulings-impacting-finance-sector</t>
         </is>
@@ -4432,41 +4668,46 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Калькулятор полной стоимости займа до заявки + self-service досрочного погашения.</t>
+          <t>Калькулятор полной стоимости займа (ставка и комиссия за выдачу) прямо на странице заявки, до подачи. Результат: уходят жалобы «комиссию не показали заранее».</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
+          <t>Self-service досрочного погашения: точная сумма на сегодня, график, оплата онлайн. Результат: меньше трений и обращений.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
           <t>N6, N3</t>
         </is>
       </c>
-      <c r="K48" s="4" t="inlineStr">
+      <c r="L48" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>CEO Lisa Jacobs (объявлен преемник 09/2026); IR Tony Nicol</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>ir@fundingcircle.com</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr"/>
-      <c r="Q48" s="2" t="inlineStr">
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/fundingcircle.com?page=4</t>
         </is>
@@ -4513,41 +4754,46 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Трекер жалоб со статусом для клиента и SLA + ответы на отзывы.</t>
+          <t>Трекер жалоб с публичным статусом для клиента и SLA. Цель — закрывать жалобы быстрее нынешних 6+ недель.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
+          <t>Модуль ответов на отзывы Trustpilot с AI-черновиками (сейчас отвечают лишь на 63% негатива) и раздельная аналитика отзывов брокеров и инвесторов.</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
           <t>N4, N2</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="L49" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>CEO Rod Lockhart; IR Chris Semple</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>investorrelations@lendinvest.com (IR); complaints@lendinvest.com (жалобы)</t>
         </is>
       </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
           <t>+44 20 3747 4187</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="2" t="inlineStr">
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr">
         <is>
           <t>https://ca.trustpilot.com/review/lendinvest.com?page=6</t>
         </is>
@@ -4594,41 +4840,46 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Клиентский портал со статусом жалобы/претензии и документами + умная маршрутизация обращений.</t>
+          <t>Клиентский портал: все документы по договору и полису, статус жалобы, защищённые сообщения. Результат: в портале будет не «только договор», а всё нужное.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
+          <t>Умная маршрутизация обращений: тема определяется автоматически, обращение уходит в нужную команду, клиент получает прогноз срока. Результат: меньше «8 недель на жалобу».</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="L50" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>CEO Mike Morgan</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>IR@closebrothers.com; Company.Secretary@closebrothers.com</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>first.last@closebrothers.com (Clay, не проверено)</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>020 7655 3100; 10 Crown Place, London EC2A 4FT</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr"/>
-      <c r="Q50" s="2" t="inlineStr">
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>https://trustpilot.com/review/closebrothers.com</t>
         </is>
@@ -4675,45 +4926,50 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>PWA/мобильный кабинет для сберегательных счетов + ускорение онлайн-заявки.</t>
+          <t>PWA-кабинет для сберегательных счетов Kent Reliance: баланс, вывод, выписки с телефона. Альтернатива отсутствующему мобильному приложению.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
+          <t>Аудит и ускорение онлайн-заявки (сейчас ~1 час вместо обещанных 10 минут), плюс отслеживание статуса вывода и закрытия счёта для клиента.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
           <t>N3, N4</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
+      <c r="L51" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>CEO Enrique Alvarez Labiano (с 09/2026); IR Alexander Holcroft</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>osbrelations@osb.co.uk</t>
         </is>
       </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
           <t>01634 838 973</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr">
+      <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>Новый CEO.</t>
         </is>
       </c>
-      <c r="Q51" s="2" t="inlineStr">
+      <c r="R51" s="2" t="inlineStr">
         <is>
           <t>https://nz.trustpilot.com/review/www.kentreliance.co.uk</t>
         </is>
@@ -4760,29 +5016,29 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Аудит производительности логина app + мониторинг отзывов app-сторов.</t>
+          <t>Аудит производительности входа в приложение Spring на Android (вход висит ~40 секунд): профилирование и список исправлений.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
+          <t>Мониторинг отзывов приложения и статус-страница при сбоях, как это было 1 апреля, чтобы клиенты узнавали о проблеме раньше, чем начинают жаловаться.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
           <t>N3, N2</t>
         </is>
       </c>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="L52" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>CEO Nigel Terrington (проверить 2026)</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -4790,11 +5046,16 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
           <t>+44 121 712 2323; Solihull B91 3QJ</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr">
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr">
         <is>
           <t>https://at.trustpilot.com/review/spring-savings.co.uk</t>
         </is>
@@ -4841,45 +5102,50 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Упрощение логина и смены привязанного счёта + мобильный кабинет.</t>
+          <t>Упрощение входа и смены привязанного счёта онлайн: меньше шагов, понятные ошибки, сохранение устройства.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
+          <t>Мобильный кабинет (PWA) для сберегательных счетов плюс анализ причин роста 1★ отзывов (+50% за 90 дней).</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>CEO Marcelino Castrillo (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>— (не найден в рамках лимита поиска)</t>
         </is>
       </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
           <t>shawbrook.co.uk</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr">
+      <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>Проверить статус листинга.</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="inlineStr">
+      <c r="R53" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/shawbrook.co.uk ; https://smartmoneypeople.com/shawbrook-reviews/product/savings?page=56</t>
         </is>
@@ -4926,41 +5192,46 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>AI-ассистент поддержки 1-й линии + аналитика крэшей по отзывам.</t>
+          <t>AI-ассистент поддержки 1-й линии по платформе: вход, верификация, ввод и вывод денег, с передачей сложных случаев человеку. Результат: уходят жалобы «бот не помогает».</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
+          <t>Аналитика крэшей и отзывов Android-приложения: кластеры проблем по версиям и устройствам с приоритетами для разработки.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
           <t>N1, N3</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>CEO Lord Peter Cruddas (основатель; проверить); Deputy CEO David Fineberg</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>investor.relations@cmcmarkets.com; r.tooley@cmcmarkets.com (Co Sec)</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>initial.last@cmcmarkets.com (из опубл. адреса)</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr">
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr">
         <is>
           <t>https://trustpilot.com/review/www.cmcmarkets.com?page=3 ; https://brokerchooser.com/broker-reviews/cmc-markets-review</t>
         </is>
@@ -5007,34 +5278,34 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Прозрачный трекер перевода (этапы, кто задерживает) + персонализированные апдейты.</t>
+          <t>Прозрачный трекер перевода пенсии: этапы, у какого провайдера застряло, сколько обычно занимает, автоматические напоминания провайдеру.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
+          <t>Персонализированные апдейты вместо шаблонных писем: AI готовит понятное объяснение конкретной задержки для клиента.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
           <t>N1, N4</t>
         </is>
       </c>
-      <c r="K55" s="4" t="inlineStr">
+      <c r="L55" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>CEO Romi Savova; CFO Christoph Martin</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>investor@pensionbee.com (IR); press@pensionbee.com</t>
         </is>
       </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -5042,10 +5313,15 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
           <t>Сильный продукт — продавать точечное улучшение.</t>
         </is>
       </c>
-      <c r="Q55" s="2" t="inlineStr">
+      <c r="R55" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/pensionbee.com?page=7</t>
         </is>
@@ -5092,41 +5368,46 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-загрузка документов NCB с напоминаниями до отмены + статус претензии.</t>
+          <t>Онлайн-загрузка подтверждения NCB с напоминаниями за 14, 7 и 3 дня до отмены полиса. Результат: меньше отмен «не прислал документ».</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
+          <t>Статус претензии онлайн (особенно non-fault): этапы, что делает страховщик, ожидаемые сроки. Результат: меньше ощущения, что за клиента не борются.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
           <t>N4, N1</t>
         </is>
       </c>
-      <c r="K56" s="4" t="inlineStr">
+      <c r="L56" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>CEO Geoff Carter (проверить 2026)</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>feedback@sabre.co.uk (из ответов на Trustpilot); IR — форма на sabreplc.co.uk</t>
         </is>
       </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
           <t>+44 330 024 4696</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr"/>
-      <c r="Q56" s="2" t="inlineStr">
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/sabre.co.uk?page=5</t>
         </is>
@@ -5173,41 +5454,46 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Сверка счетов и детектор аномальных начислений + объяснение счёта простым языком.</t>
+          <t>Детектор аномальных начислений: сверка счёта с активными услугами, алерт при плате за удалённую услугу или за отменённое отключение.</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
+          <t>«Объясни мой счёт»: AI простым языком разбирает строки счёта, отвечает на вопросы и сразу создаёт спор по спорной строке.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
           <t>N6, N1</t>
         </is>
       </c>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="L57" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>CEO Stuart Burnett; IR Louise Rich</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>louise.rich@uw.co.uk (IR); utilitywarehouse@lansons.com (медиа)</t>
         </is>
       </c>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>first.last@uw.co.uk (из опубл. адреса) → stuart.burnett@uw.co.uk (не проверено)</t>
         </is>
       </c>
-      <c r="O57" s="2" t="inlineStr">
+      <c r="P57" s="2" t="inlineStr">
         <is>
           <t>IR +44 7486 895017</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr"/>
-      <c r="Q57" s="2" t="inlineStr">
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/uw.co.uk?page=2</t>
         </is>
@@ -5254,41 +5540,46 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Портал споров по счетам со статусом + честная система сбора отзывов (риск DMCC: фейковые отзывы запрещены с 04/2025).</t>
+          <t>Портал споров по счетам для бизнес-клиентов: номер дела, статус, сроки, загрузка показаний и документов. Результат: никаких «3 лет войны» без ответа.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
+          <t>Честная система сбора отзывов (приглашение всех клиентов, без фильтрации) после истории с подозрениями в накрутке. Снижает риски по DMCC Act, где фейковые отзывы запрещены.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
           <t>N4, N2</t>
         </is>
       </c>
-      <c r="K58" s="4" t="inlineStr">
+      <c r="L58" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>CEO Bobby Kalar; CFO Andy Simpson</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>yugroup@tulchangroup.com (PR, 2022 — проверить)</t>
         </is>
       </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
           <t>+44 115 975 8258; yugroupplc.com</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr"/>
-      <c r="Q58" s="2" t="inlineStr">
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr">
         <is>
           <t>https://ie.trustpilot.com/review/yuenergy.co.uk ; https://www.magzter.com/en/stories/newspaper/Nottingham-Post/EXEMPLOYEE-CLAIMS-ENERGY-FIRM-PAID-STAFF-TO-WRITE-FAKE-REVIEWS</t>
         </is>
@@ -5335,34 +5626,34 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-подача показаний и объяснение счёта + портал спора по счёту (под новую платформу).</t>
+          <t>Онлайн-подача показаний и пересчёт расчётного счёта: фото счётчика, распознавание цифр, мгновенный новый счёт.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
+          <t>Портал спора по счёту и уведомления об установке смарт-счётчика, в связке с новой биллинговой платформой. Результат: меньше жалоб в CCW.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
           <t>N4, N6</t>
         </is>
       </c>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="L59" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>CEO Keith Haslett (с 04/2026); Head IR James Found</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr">
         <is>
           <t>— (IR по телефону +44 7970 066634)</t>
         </is>
       </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -5370,10 +5661,15 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
           <t>Регулируемая монополия — тендеры.</t>
         </is>
       </c>
-      <c r="Q59" s="2" t="inlineStr">
+      <c r="R59" s="2" t="inlineStr">
         <is>
           <t>https://www.itv.com/news/2026-10-07/south-west-water-owner-pennon-calls-on-investors-to-help-fund-overhaul ; https://ca.trustpilot.com/review/southwestwater.co.uk</t>
         </is>
@@ -5420,41 +5716,46 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Self-service баланса и активации + напоминания об истечении срока.</t>
+          <t>Self-service баланса: проверка, перенос баланса карты в онлайн-аккаунт, активация онлайн, без звонков и платной замены карты за £8.90.</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
+          <t>Напоминания об истечении срока подарочной карты за 60, 30 и 7 дней. Результат: меньше «сгоревших» балансов и злых отзывов.</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
           <t>N1, N6</t>
         </is>
       </c>
-      <c r="K60" s="4" t="inlineStr">
+      <c r="L60" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>CEO Nick Wiles</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t>— (через FGS Global)</t>
         </is>
       </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr"/>
-      <c r="Q60" s="2" t="inlineStr">
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr">
         <is>
           <t>https://nl.trustpilot.com/review/love2shop.co.uk</t>
         </is>
@@ -5501,41 +5802,46 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Трекер статуса кэшбэка для пользователя + починка логина/сброса пароля.</t>
+          <t>Трекер статуса кэшбэка для пользователя: подтверждено, ожидает или выплачено, с ожидаемой датой. Результат: меньше вопросов «жду 7 месяцев».</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
+          <t>Аудит и починка входа и сброса пароля, плюс AI-ответы на типовые обращения пользователей MSE и Energy Club.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
           <t>N1, N3</t>
         </is>
       </c>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="L61" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="M61" s="2" t="inlineStr">
         <is>
           <t>CEO Peter Duffy; CFO Niall McBride; Head IR Jennifer Cooke</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr">
+      <c r="N61" s="2" t="inlineStr">
         <is>
           <t>jennifer.cooke@monygroup.com (IR); niall.mcbride@monygroup.com (CFO)</t>
         </is>
       </c>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>first.last@monygroup.com (из опубл. адресов) → peter.duffy@monygroup.com (не проверено)</t>
         </is>
       </c>
-      <c r="O61" s="2" t="inlineStr">
+      <c r="P61" s="2" t="inlineStr">
         <is>
           <t>IR 0203 846 2034</t>
         </is>
       </c>
-      <c r="P61" s="2" t="inlineStr"/>
-      <c r="Q61" s="2" t="inlineStr">
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr">
         <is>
           <t>https://ca.trustpilot.com/review/www.moneysavingexpert.com?page=6</t>
         </is>
@@ -5582,45 +5888,50 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Трекер выплат баллов + прозрачные причины блокировки и апелляция онлайн.</t>
+          <t>Трекер выплат баллов панелистам: статус запроса, ожидаемая дата и автоматическая эскалация, если деньги не пришли.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
+          <t>Прозрачные причины блокировки аккаунта и онлайн-апелляция, плюс аудит скорости сайта панели.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
           <t>N1, N3</t>
         </is>
       </c>
-      <c r="K62" s="4" t="inlineStr">
+      <c r="L62" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>CEO Stephan Shakespeare → Wayne Levings (designate с 01.11.2026); IR Hannah Jethwani</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>investor.relations@yougov.com</t>
         </is>
       </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
           <t>020 7012 6000</t>
         </is>
       </c>
-      <c r="P62" s="2" t="inlineStr">
+      <c r="Q62" s="2" t="inlineStr">
         <is>
           <t>Смена CEO.</t>
         </is>
       </c>
-      <c r="Q62" s="2" t="inlineStr">
+      <c r="R62" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/yougov.co.uk ; https://www.productreview.com.au/listings/yougov</t>
         </is>
@@ -5667,41 +5978,46 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Аудит Core Web Vitals и «тяжёлых» рекламных слотов + A/B-тест облегчённой страницы.</t>
+          <t>Аудит Core Web Vitals и рекламной нагрузки на топ-статьях: какие слоты и pop-up убивают скорость и сколько трафика это стоит.</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
+          <t>A/B-тест облегчённого шаблона статьи (меньше pop-up, ленивая загрузка рекламы) с измерением выручки и глубины просмотра.</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="L63" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>CEO Piers North; CFO Darren Fisher; IR Jo Britten</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>investorrelations@reachplc.com</t>
         </is>
       </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P63" s="2" t="inlineStr"/>
-      <c r="Q63" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr">
         <is>
           <t>https://pressgazette.co.uk/publishers/regional-newspapers/manchester-evening-news-men-trials-premium-app-with-metered-paywall/ ; https://www.holdthefrontpage.co.uk/2025/news/reach-boss-defends-free-to-access-websites-but-admits-user-experience-must-improve</t>
         </is>
@@ -5748,29 +6064,29 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Аудит скорости и рекламной нагрузки + лёгкие шаблоны статей.</t>
+          <t>Аудит скорости и автоплея видео на TechRadar и What Hi-Fi: влияние на отказы и ad-block с конкретными рекомендациями.</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
+          <t>Лёгкий шаблон статьи и настройки автоплея (по клику, без звука) с A/B-тестом. Результат: меньше ad-block и больше лояльных читателей.</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="K64" s="5" t="inlineStr">
+      <c r="L64" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>CEO Kevin Li Ying (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -5778,15 +6094,20 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
           <t>futureplc.com</t>
         </is>
       </c>
-      <c r="P64" s="2" t="inlineStr">
+      <c r="Q64" s="2" t="inlineStr">
         <is>
           <t>Доказательства средние (форумы).</t>
         </is>
       </c>
-      <c r="Q64" s="2" t="inlineStr">
+      <c r="R64" s="2" t="inlineStr">
         <is>
           <t>https://digiday.com/publishers/future-cuts-100-ad-impressions-year-improve-quality-placate-ad-blocker-users ; https://forums.whathifi.com/threads/whf-site-and-bauer-in-general.114566/latest</t>
         </is>
@@ -5833,41 +6154,46 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>QA-аудит плеера и логики рекламных вставок + мониторинг отзывов app-сторов.</t>
+          <t>QA-аудит плеера на основных устройствах: буферизация, вылеты после рекламы, повтор рекламы после паузы и перемотки, с отчётом и приоритетами.</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
+          <t>Мониторинг отзывов приложений и Trustpilot с алертами во время трансляций (как на ЧМ-2026) и публичная статус-страница сбоев.</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
           <t>N3, N2</t>
         </is>
       </c>
-      <c r="K65" s="4" t="inlineStr">
+      <c r="L65" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>CEO Rufus Radcliffe (ex-ITVX); Head of Comms Kirstin Stevenson</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr">
         <is>
           <t>— (см. stvplc.tv/newsroom)</t>
         </is>
       </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P65" s="2" t="inlineStr"/>
-      <c r="Q65" s="2" t="inlineStr">
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr">
         <is>
           <t>https://ie.trustpilot.com/review/www.stv.tv</t>
         </is>
@@ -5914,45 +6240,50 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>AI-поддержка по статусу вывода/верификации + мониторинг багов app.</t>
+          <t>AI-ассистент поддержки по статусу вывода и верификации: объясняет, что нужно для вывода, и показывает этап проверки.</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
+          <t>Мониторинг багов приложения Mecca на Android по отзывам (бонусы, глюки) с отчётом для разработки.</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
           <t>N1, N2</t>
         </is>
       </c>
-      <c r="K66" s="5" t="inlineStr">
+      <c r="L66" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>CEO Richard Harris (с 07/2026); Corp Affairs &amp; IR David Williams</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>david.williams@rank.com (IR); chloe.barry@rank.com (Co Sec)</t>
         </is>
       </c>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>first.last@rank.com (из опубл. адресов)</t>
         </is>
       </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
           <t>Гемблинг — строгий комплаенс.</t>
         </is>
       </c>
-      <c r="Q66" s="2" t="inlineStr">
+      <c r="R66" s="2" t="inlineStr">
         <is>
           <t>https://www.gambling.com/uk/online-casinos/mecca</t>
         </is>
@@ -5999,24 +6330,24 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Прозрачный статус вывода/KYC для клиента.</t>
+          <t>Страница статуса вывода средств и KYC: какие документы нужны, этап проверки, сроки. Результат: меньше «выиграл — деньги заблокировали».</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
+          <t>AI-разбор отзывов William Hill (рейтинг 1.2) по причинам: вывод, KYC, ограничения, для приоритизации исправлений после смены владельца.</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
           <t>N1, N4</t>
         </is>
       </c>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="L67" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -6029,15 +6360,20 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
           <t>evokeplc.com</t>
         </is>
       </c>
-      <c r="P67" s="2" t="inlineStr">
+      <c r="Q67" s="2" t="inlineStr">
         <is>
           <t>Согласовано поглощение Bally's Intralot (£243m, закрытие Q4 2026) — низкий приоритет.</t>
         </is>
       </c>
-      <c r="Q67" s="2" t="inlineStr">
+      <c r="R67" s="2" t="inlineStr">
         <is>
           <t>https://ca.trustpilot.com/review/williamhill.com?page=2 ; https://www.ajbell.co.uk/news/articles/evoke-agrees-ps243-million-takeover-offer-ballys-intralot</t>
         </is>
@@ -6084,41 +6420,46 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Портал арендатора/арендодателя: заявки на ремонт с фото, статус, SLA + ответы на отзывы.</t>
+          <t>Портал арендатора: заявка на ремонт с фото, статус, сроки, переписка с арендодателем в одном месте. Результат: «не можем связаться с арендодателем» перестаёт быть ответом.</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
+          <t>Портал арендодателя (отчёты, статусы, обязательные сроки ответа на письма) плюс модуль ответов на отзывы (сейчас на негатив не отвечают).</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
           <t>N5, N2</t>
         </is>
       </c>
-      <c r="K68" s="4" t="inlineStr">
+      <c r="L68" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>CEO Guy Gittins; IR Muhammad Patel</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="N68" s="2" t="inlineStr">
         <is>
           <t>investor@foxtonsgroup.co.uk (IR, 2022 — проверить)</t>
         </is>
       </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
           <t>+44 20 7893 6261</t>
         </is>
       </c>
-      <c r="P68" s="2" t="inlineStr"/>
-      <c r="Q68" s="2" t="inlineStr">
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/www.foxtons.co.uk?page=9</t>
         </is>
@@ -6165,41 +6506,46 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Единый трекер ремонтов для всех франчайзи + сбор и ответы на отзывы по офисам.</t>
+          <t>Единый трекер ремонтов для всех франчайзи-офисов Belvoir: заявка с фото, подрядчик, SLA, статус для арендатора и арендодателя.</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
+          <t>Модуль сбора и ответов на отзывы по каждому офису с рейтингом франчайзи. Результат: Trustpilot 2.5 растёт, а сеть видит проблемные офисы.</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
           <t>N5, N2</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
+      <c r="L69" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>CEO Gareth Samples</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="N69" s="2" t="inlineStr">
         <is>
           <t>company.secretary@propertyfranchise.co.uk</t>
         </is>
       </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
           <t>01202 405 549; 2 St Stephen's Court, Bournemouth BH2 6LA</t>
         </is>
       </c>
-      <c r="P69" s="2" t="inlineStr"/>
-      <c r="Q69" s="2" t="inlineStr">
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr">
         <is>
           <t>https://nl.trustpilot.com/review/www.belvoir.co.uk ; https://thecourier.co.uk/fp/news/dundee/5048203/belvoir-dundee-police-action-legal-victory</t>
         </is>
@@ -6246,41 +6592,46 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Портал жалоб/ремонтов для lettings-клиентов франчайзи со статусом.</t>
+          <t>Портал жалоб для клиентов lettings со статусом по стадиям (1, 2, омбудсмен) и сроками. Результат: меньше дел, доходящих до The Property Ombudsman.</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
+          <t>Трекер ремонтов (плесень, протечки) и автоматическое снятие объекта с рекламы после выезда арендатора.</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
           <t>N5, N4</t>
         </is>
       </c>
-      <c r="K70" s="4" t="inlineStr">
+      <c r="L70" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t>CEO Adam Castleton; CFO David Tilak; IR Phil Clark</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t>investorrelations@lslps.co.uk</t>
         </is>
       </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P70" s="2" t="inlineStr"/>
-      <c r="Q70" s="2" t="inlineStr">
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr">
         <is>
           <t>https://au.trustpilot.com/review/www.lslps.co.uk ; https://de.trustpilot.com/review/reedsrains.co.uk</t>
         </is>
@@ -6327,41 +6678,46 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Система ответов на отзывы для франчайзи + сбор отзывов после сделки.</t>
+          <t>Система ответов на отзывы для франчайзи: AI-черновики, единый стиль, SLA. Цель — отвечать на 100% негатива вместо 53–60%.</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
+          <t>Автоматический сбор отзывов после сделки или заселения плюс внутренний рейтинг офисов. Результат: защита бренда без попыток удалять отзывы.</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="K71" s="3" t="inlineStr">
+      <c r="L71" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L71" s="2" t="inlineStr">
+      <c r="M71" s="2" t="inlineStr">
         <is>
           <t>CEO Dominic Agace (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr">
+      <c r="N71" s="2" t="inlineStr">
         <is>
           <t>— (не найден в рамках лимита поиска)</t>
         </is>
       </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
           <t>winkworth.co.uk</t>
         </is>
       </c>
-      <c r="P71" s="2" t="inlineStr"/>
-      <c r="Q71" s="2" t="inlineStr">
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr">
         <is>
           <t>https://nl-be.trustpilot.com/review/www.winkworth.co.uk ; https://www.getagent.co.uk/branch/winkworth-shepherds-bush-acton-w12/8159</t>
         </is>
@@ -6408,41 +6764,46 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Клиентский портал снаггинга: заявка с фото, слоты визита, статус, закрытие с подписью.</t>
+          <t>Клиентский портал снаггинга: дефект с фото, выбор слота визита, статус, закрытие с подписью покупателя.</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
+          <t>Аналитика повторяющихся дефектов по участкам и подрядчикам (окна, отопление, кровля) плюс публичные ответы на отзывы (сейчас их нет).</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
           <t>N5, N2</t>
         </is>
       </c>
-      <c r="K72" s="3" t="inlineStr">
+      <c r="L72" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="M72" s="2" t="inlineStr">
         <is>
           <t>CEO Innes Smith</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
           <t>first.last@springfield.co.uk (Prospeo, 68%) → innes.smith@springfield.co.uk (не проверено)</t>
         </is>
       </c>
-      <c r="O72" s="2" t="inlineStr">
+      <c r="P72" s="2" t="inlineStr">
         <is>
           <t>+44 1343 552550; Elgin IV30 6GR</t>
         </is>
       </c>
-      <c r="P72" s="2" t="inlineStr"/>
-      <c r="Q72" s="2" t="inlineStr">
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/springfield.co.uk/location/knockomie-braes</t>
         </is>
@@ -6489,29 +6850,29 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Трекер aftercare/снаггинга на 2 года гарантии + напоминания и отчётность.</t>
+          <t>Трекер aftercare на весь 2-летний гарантийный период: заявки, сроки, напоминания и отчётность по каждой стройке.</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
+          <t>Автоматические чек-ины с покупателем через 1, 6 и 12 месяцев после заселения, чтобы находить проблемы до того, как они станут жалобами.</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="K73" s="4" t="inlineStr">
+      <c r="L73" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>CEO Graham Prothero (с 04/2025)</t>
         </is>
       </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -6519,11 +6880,16 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
           <t>+44 114 261 2900; mjgleesonplc.com</t>
         </is>
       </c>
-      <c r="P73" s="2" t="inlineStr"/>
-      <c r="Q73" s="2" t="inlineStr">
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr">
         <is>
           <t>https://ch.trustpilot.com/review/gleesonhomes.co.uk</t>
         </is>
@@ -6570,41 +6936,46 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Портал aftercare со статусом и фото + аналитика повторяющихся дефектов по участкам.</t>
+          <t>Портал aftercare со статусом и фото: дренаж, газоны, дефекты. Покупатель видит, кто и когда исправит.</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
+          <t>Аналитика повторяющихся дефектов по участкам для стройки и закупок. Результат: меньше проблем через 3–10 лет после сдачи.</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
           <t>N5, N2</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
+      <c r="L74" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>CEO Martyn Clark; CFO Bill Floydd; IR Jenny Matthews</t>
         </is>
       </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr">
         <is>
           <t>— (IR по телефону +44 7557 842720; PR Teneo)</t>
         </is>
       </c>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P74" s="2" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr">
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/crestnicholson.com</t>
         </is>
@@ -6651,29 +7022,29 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Портал снаггинга/жалоб с SLA для покупателей + аналитика дефектов.</t>
+          <t>Портал снаггинга и жалоб с SLA для покупателей Vistry и Countryside Homes: фото, статус, сроки.</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
+          <t>Дашборд качества по стройкам на основе дефектов и отзывов (рейтинг 1.5): какие площадки и подрядчики портят репутацию.</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
           <t>N5, N2</t>
         </is>
       </c>
-      <c r="K75" s="5" t="inlineStr">
+      <c r="L75" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L75" s="2" t="inlineStr">
+      <c r="M75" s="2" t="inlineStr">
         <is>
           <t>CEO Greg Fitzgerald (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -6681,15 +7052,20 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
           <t>vistrygroup.co.uk</t>
         </is>
       </c>
-      <c r="P75" s="2" t="inlineStr">
+      <c r="Q75" s="2" t="inlineStr">
         <is>
           <t>Крупная компания.</t>
         </is>
       </c>
-      <c r="Q75" s="2" t="inlineStr">
+      <c r="R75" s="2" t="inlineStr">
         <is>
           <t>https://ca.trustpilot.com/review/vistrygroup.co.uk ; https://www.yorkshirepost.co.uk/lifestyle/homes-and-gardens/new-build-housing-best-and-worst-rated-companies-based-on-reviews-5223425</t>
         </is>
@@ -6736,29 +7112,29 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Трекер дефектов с фото и таймстемпами в гарантийный период.</t>
+          <t>Трекер дефектов с фото и таймстемпами в гарантийный период. Фиксирует, когда о проблеме сообщили, чтобы не было отказов «гарантия закончилась».</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
+          <t>Мониторинг отзывов вне Trustpilot (reviews.io 1.2) и эскалация повторяющихся проблем (дренаж и т.п.) руководителям регионов.</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="K76" s="5" t="inlineStr">
+      <c r="L76" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>CEO Dean Finch (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -6766,15 +7142,20 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
           <t>persimmonhomes.com</t>
         </is>
       </c>
-      <c r="P76" s="2" t="inlineStr">
+      <c r="Q76" s="2" t="inlineStr">
         <is>
           <t>Крупная компания.</t>
         </is>
       </c>
-      <c r="Q76" s="2" t="inlineStr">
+      <c r="R76" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/persimmonhomes.com ; https://www.reviews.io/company-reviews/store/persimmonhomes/EJ</t>
         </is>
@@ -6821,41 +7202,46 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Заявки на ремонт с фото и ETA в app + прозрачный расчёт возврата депозита.</t>
+          <t>Заявки на ремонт в приложении с фото, ETA и уведомлением о визите. Результат: меньше «ремонт месяцами».</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
+          <t>Прозрачный расчёт возврата депозита: фото при заселении и выезде, список удержаний с доказательствами.</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
           <t>N5, N3</t>
         </is>
       </c>
-      <c r="K77" s="5" t="inlineStr">
+      <c r="L77" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L77" s="2" t="inlineStr">
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>CEO Joe Lister; CFO Mike Burt</t>
         </is>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr">
         <is>
           <t>— (тел. +44 117 302 7005; пресс +44 117 450 6300)</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P77" s="2" t="inlineStr"/>
-      <c r="Q77" s="2" t="inlineStr">
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr">
         <is>
           <t>https://ie.trustpilot.com/review/www.unitestudents.com ; https://vibemystay.pages.dev/provider/unite-students</t>
         </is>
@@ -6902,29 +7288,29 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Трекер обещанных бонусов/кэшбэка + заявки на доступ/ремонт с SLA.</t>
+          <t>Трекер обещанных бонусов и кэшбэка студентам: что обещано, когда выплачено, автоматическое напоминание команде.</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
+          <t>Заявки на доступ (ключ-карты) и ремонт с SLA плюс ускорение ответов на негатив (сейчас больше месяца).</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
           <t>N5, N1</t>
         </is>
       </c>
-      <c r="K78" s="4" t="inlineStr">
+      <c r="L78" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr">
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>CEO Alex Pease; CFO Simon Jones</t>
         </is>
       </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -6932,15 +7318,20 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
           <t>+44 20 3617 4453</t>
         </is>
       </c>
-      <c r="P78" s="2" t="inlineStr">
+      <c r="Q78" s="2" t="inlineStr">
         <is>
           <t>Проверить, кто сейчас управляет брендом HfS.</t>
         </is>
       </c>
-      <c r="Q78" s="2" t="inlineStr">
+      <c r="R78" s="2" t="inlineStr">
         <is>
           <t>https://es.trustpilot.com/review/wearehomesforstudents.com</t>
         </is>
@@ -6987,41 +7378,46 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Уведомления жильцам о работах в доме + заявки на ремонт со статусом.</t>
+          <t>Уведомления жильцам о строительных работах в доме: график, шум, отключения, через SMS и приложение.</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
+          <t>Заявки на ремонт со статусом плюс программа лояльности для долгосрочных арендаторов (прозрачная индексация аренды).</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="K79" s="5" t="inlineStr">
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L79" s="2" t="inlineStr">
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>CEO Helen Gordon (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M79" s="2" t="inlineStr">
+      <c r="N79" s="2" t="inlineStr">
         <is>
           <t>— (не найден в рамках лимита поиска)</t>
         </is>
       </c>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
           <t>graingerplc.co.uk</t>
         </is>
       </c>
-      <c r="P79" s="2" t="inlineStr"/>
-      <c r="Q79" s="2" t="inlineStr">
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/graingerplc.co.uk?page=7</t>
         </is>
@@ -7068,41 +7464,46 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-запись на визит, напоминания, фото-отчёт о выполненном ремонте для жильца и совета.</t>
+          <t>Онлайн-запись на визит ремонтника с напоминаниями жильцу и окном «мастер в пути». Результат: меньше пропущенных визитов.</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
+          <t>Фото-отчёт о выполненном ремонте для жильца и совета (до и после, подпись жильца). Даёт доказательства качества при продлении контрактов.</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="K80" s="4" t="inlineStr">
+      <c r="L80" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L80" s="2" t="inlineStr">
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>CEO Lucy Tilley (не подтверждено — проверить); Co Sec Ben Westran</t>
         </is>
       </c>
-      <c r="M80" s="2" t="inlineStr">
+      <c r="N80" s="2" t="inlineStr">
         <is>
           <t>info@mearsgroup.co.uk (общий, может быть устаревшим)</t>
         </is>
       </c>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
           <t>+44 1452 634600</t>
         </is>
       </c>
-      <c r="P80" s="2" t="inlineStr"/>
-      <c r="Q80" s="2" t="inlineStr">
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr">
         <is>
           <t>https://towerhamletsslice.co.uk/?p=60989 ; https://londonrentersunion.org/2025/tell-tower-hamlets-council-cut-mears/</t>
         </is>
@@ -7149,34 +7550,34 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Статус-страница и умный триаж обращений; автоматизация типовых ответов по делам.</t>
+          <t>Статус-страница и умный триаж обращений участников пенсионной схемы: автоматическое определение срочных дел (пенсия не выплачена) и прогноз срока.</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
+          <t>Само-восстановление доступа к порталу (16 000 заблокированных участников) плюс AI-автоматизация типовых ответов по делам.</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
           <t>N4, N1</t>
         </is>
       </c>
-      <c r="K81" s="5" t="inlineStr">
+      <c r="L81" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L81" s="2" t="inlineStr">
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>CEO Adolfo Hernandez; IR Helen Parris / Stephanie Little</t>
         </is>
       </c>
-      <c r="M81" s="2" t="inlineStr">
+      <c r="N81" s="2" t="inlineStr">
         <is>
           <t>IRteam@capita.co.uk (IR); media@capita.co.uk</t>
         </is>
       </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -7184,10 +7585,15 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
           <t>Огромная организация — заходить через субподряд/партнёра.</t>
         </is>
       </c>
-      <c r="Q81" s="2" t="inlineStr">
+      <c r="R81" s="2" t="inlineStr">
         <is>
           <t>https://www.professionalpensions.com/news/4524700/capita-issues-apology-civil-service-pensions-scheme-challenges ; https://www.pensionsage.com/pa/Capita-targets-June-service-recovery-as-CSPS-backlog-falls-to-56-000-cases.php</t>
         </is>
@@ -7234,45 +7640,50 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Напоминания о приёме/правилах опоздания + трекер жалоб пациента.</t>
+          <t>Напоминания пациентам о приёме, правилах опоздания и штрафах (SMS и email за 48 и 2 часа). Результат: меньше споров о штрафах £300.</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
+          <t>Трекер жалоб пациента: статус, ответственный, сроки, и отчёт для руководства по клиникам.</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
           <t>N4, N1</t>
         </is>
       </c>
-      <c r="K82" s="5" t="inlineStr">
+      <c r="L82" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L82" s="2" t="inlineStr">
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>Interim CEO Sir David Sloman (с 09/2026); IR Amie Gramlick</t>
         </is>
       </c>
-      <c r="M82" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>investors@spirehealthcare.com; companysecretary@spirehealthcare.com</t>
         </is>
       </c>
-      <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
           <t>+44 800 169 1777</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr">
+      <c r="Q82" s="2" t="inlineStr">
         <is>
           <t>Смена CEO.</t>
         </is>
       </c>
-      <c r="Q82" s="2" t="inlineStr">
+      <c r="R82" s="2" t="inlineStr">
         <is>
           <t>https://nz.trustpilot.com/review/www.spirehealthcare.com</t>
         </is>
@@ -7319,34 +7730,34 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Очередь с прогнозом времени ожидания + безопасный AI-триаж/контент на время ожидания (с клиницистами).</t>
+          <t>Очередь с прогнозом ожидания и сохранением места, без выкидывания из чата после долгого ожидания.</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
+          <t>Безопасный контент и самопомощь на время ожидания плюс триаж срочности под надзором клиницистов. Результат: лучше аргументы при продлении контрактов NHS.</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
           <t>N3, N1</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr">
+      <c r="L83" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L83" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>CEO Tim Barker (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>complaints@kooth.com (жалобы)</t>
         </is>
       </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -7354,10 +7765,15 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
           <t>Чувствительная сфера: только с клиническим надзором.</t>
         </is>
       </c>
-      <c r="Q83" s="2" t="inlineStr">
+      <c r="R83" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/kooth.com?page=2 ; https://www.cnwl.nhs.uk/news/tell-us-what-you-think-kooth</t>
         </is>
@@ -7404,41 +7820,46 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Быстрый чекаут с Apple/Google Pay + проверка актуальности скидок партнёров.</t>
+          <t>Быстрый чекаут подарочных карт с Apple Pay и Google Pay в приложении Hapi. Результат: покупка за секунды вместо долгого оформления.</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
+          <t>Автоматическая проверка актуальности скидок партнёров (работает ли скидка в магазине, верен ли процент) с алертами. Результат: меньше жалоб на «обманные» скидки.</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="K84" s="3" t="inlineStr">
+      <c r="L84" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L84" s="2" t="inlineStr">
+      <c r="M84" s="2" t="inlineStr">
         <is>
           <t>CEO Paula Constant; CFO Matthew Cohen (06/2026)</t>
         </is>
       </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="N84" s="2" t="inlineStr">
         <is>
           <t>personalgroup@almastrategic.com (IR-агентство Alma)</t>
         </is>
       </c>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P84" s="2" t="inlineStr"/>
-      <c r="Q84" s="2" t="inlineStr">
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr">
         <is>
           <t>https://apps.apple.com/gb/app/hapi/id1377720085 ; https://ca.trustpilot.com/review/hapi.co.uk</t>
         </is>
@@ -7485,45 +7906,50 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Обмен статусом KYC между платформой и аукционными домами + портал апелляций по блокировкам.</t>
+          <t>Обмен статусом KYC между платформой и аукционными домами: покупатель проходит верификацию один раз, дом видит её результат.</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
+          <t>Портал апелляций по блокировкам аккаунтов и спорным лотам («выиграл онлайн — продали в зале») с прозрачным статусом.</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
           <t>N1, N7</t>
         </is>
       </c>
-      <c r="K85" s="4" t="inlineStr">
+      <c r="L85" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L85" s="2" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>CEO Duncan Painter (с 05/2026)</t>
         </is>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>chrisdyett@auctiontechnologygroup.com, matthewwalker@auctiontechnologygroup.com (IR); atg@fticonsulting.com (PR)</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>firstlast@auctiontechnologygroup.com (из опубл. адресов) → duncanpainter@… (не проверено)</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="P85" s="2" t="inlineStr">
         <is>
           <t>+44 7974 974690</t>
         </is>
       </c>
-      <c r="P85" s="2" t="inlineStr">
+      <c r="Q85" s="2" t="inlineStr">
         <is>
           <t>Новый CEO.</t>
         </is>
       </c>
-      <c r="Q85" s="2" t="inlineStr">
+      <c r="R85" s="2" t="inlineStr">
         <is>
           <t>https://ch.trustpilot.com/review/www.auctiontechnologygroup.com ; https://uk.trustpilot.com/review/twgaze.co.uk</t>
         </is>
@@ -7570,41 +7996,46 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Self-service изменения/возврата брони + форма жалобы со статусом.</t>
+          <t>Self-service изменения и возврата брони онлайн с понятными правилами и гарантированным письмом-подтверждением.</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
+          <t>Онлайн-форма жалобы со статусом и сроками (сейчас до 10 дней без ясности) плюс AI-черновики ответов.</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
           <t>N3, N1</t>
         </is>
       </c>
-      <c r="K86" s="5" t="inlineStr">
+      <c r="L86" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L86" s="2" t="inlineStr">
+      <c r="M86" s="2" t="inlineStr">
         <is>
           <t>Group CEO Francisco (Paco) Iglesias (с 04/2026)</t>
         </is>
       </c>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="N86" s="2" t="inlineStr">
         <is>
           <t>ir@mobicogroup.com</t>
         </is>
       </c>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
           <t>Headland (медиа)</t>
         </is>
       </c>
-      <c r="P86" s="2" t="inlineStr"/>
-      <c r="Q86" s="2" t="inlineStr">
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr">
         <is>
           <t>https://www.reviews.io/company-reviews/store/national-express ; https://ca.trustpilot.com/review/nxbus.co.uk?page=2</t>
         </is>
@@ -7651,41 +8082,46 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Офлайн-доступ к купленным билетам + статус-страница инцидентов app + мониторинг отзывов.</t>
+          <t>Офлайн-доступ к купленным билетам в приложении и восстановление аккаунта без потери билетов. Против проблем вроде обновления в мае 2026.</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
+          <t>Статус-страница инцидентов приложения и мониторинг отзывов с алертами после релизов.</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
           <t>N3, N2</t>
         </is>
       </c>
-      <c r="K87" s="5" t="inlineStr">
+      <c r="L87" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L87" s="2" t="inlineStr">
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>CEO Graham Sutherland; Head IR Marianna Bowes</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>corporate.comms@firstgroup.co.uk (2024)</t>
         </is>
       </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
           <t>IR +44 20 7404 5959</t>
         </is>
       </c>
-      <c r="P87" s="2" t="inlineStr"/>
-      <c r="Q87" s="2" t="inlineStr">
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr">
         <is>
           <t>https://parkandride.portsmouth.gov.uk/updates-to-first-bus-app/ ; https://ca.trustpilot.com/review/www.firstgroup.com?page=3</t>
         </is>
@@ -7732,29 +8168,29 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Автоматические заявки delay repay по данным о задержках.</t>
+          <t>Автоматические заявки delay repay: система сама видит задержку поезда и подаёт заявку за клиента.</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
+          <t>Мониторинг доступности страниц отмены и рефанда с алертами (в мае 2026 они не загружались).</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
           <t>N1, N6</t>
         </is>
       </c>
-      <c r="K88" s="5" t="inlineStr">
+      <c r="L88" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L88" s="2" t="inlineStr">
+      <c r="M88" s="2" t="inlineStr">
         <is>
           <t>CEO Jody Ford (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -7762,15 +8198,20 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
           <t>trainlinegroup.com</t>
         </is>
       </c>
-      <c r="P88" s="2" t="inlineStr">
+      <c r="Q88" s="2" t="inlineStr">
         <is>
           <t>Крупная tech-компания.</t>
         </is>
       </c>
-      <c r="Q88" s="2" t="inlineStr">
+      <c r="R88" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/www.thetrainline.com?page=8 ; https://www.reviews.io/company-reviews/store/thetrainline</t>
         </is>
@@ -7817,34 +8258,34 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Статус жалобы/рефанда онлайн с прогнозом срока.</t>
+          <t>Онлайн-статус жалобы и рефанда с прогнозом срока и автоматическим напоминанием, если просрочено обещание «7 дней».</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
+          <t>AI-персонализация публичных ответов на отзывы вместо скриптовых, со ссылкой на конкретное решение.</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
           <t>N4, N1</t>
         </is>
       </c>
-      <c r="K89" s="5" t="inlineStr">
+      <c r="L89" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L89" s="2" t="inlineStr">
+      <c r="M89" s="2" t="inlineStr">
         <is>
           <t>CEO Kenton Jarvis (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M89" s="2" t="inlineStr">
+      <c r="N89" s="2" t="inlineStr">
         <is>
           <t>TrustpilotReviews@easyJet.com (из ответов на Trustpilot)</t>
         </is>
       </c>
-      <c r="N89" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -7852,10 +8293,15 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
           <t>Крупная компания.</t>
         </is>
       </c>
-      <c r="Q89" s="2" t="inlineStr">
+      <c r="R89" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/www.easyjet.com?page=8</t>
         </is>
@@ -7902,29 +8348,29 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Портал возвратов с понятными правилами и авто-рефандом + проверка размерных сеток.</t>
+          <t>Портал возвратов с понятными правилами (рефанд или store credit, удержания) до оформления заказа и авто-рефандом.</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
+          <t>Проверка размерных сеток в карточках товаров и аналитика возвратов по причине «не тот размер».</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
           <t>N1, N3</t>
         </is>
       </c>
-      <c r="K90" s="5" t="inlineStr">
+      <c r="L90" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="M90" s="2" t="inlineStr">
         <is>
           <t>CEO — проверить (Michael Murray по данным 2024–2025)</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -7932,15 +8378,20 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
           <t>frasers.group</t>
         </is>
       </c>
-      <c r="P90" s="2" t="inlineStr">
+      <c r="Q90" s="2" t="inlineStr">
         <is>
           <t>Крупная, закрытая компания.</t>
         </is>
       </c>
-      <c r="Q90" s="2" t="inlineStr">
+      <c r="R90" s="2" t="inlineStr">
         <is>
           <t>https://au.trustpilot.com/review/sportsdirect.uk</t>
         </is>
@@ -7987,29 +8438,29 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Прозрачная политика возвратов в ЛК (показатель «риска блокировки», предупреждения).</t>
+          <t>Прозрачная политика возвратов в личном кабинете: индикатор «риска ограничения аккаунта» и предупреждение до блокировки.</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
+          <t>Трекер рефанда с гарантированным сроком (до 15 дней) и автоматической эскалацией при просрочке.</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
           <t>N1, N6</t>
         </is>
       </c>
-      <c r="K91" s="5" t="inlineStr">
+      <c r="L91" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L91" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>CEO José Antonio Ramos Calamonte (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -8017,15 +8468,20 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
           <t>asosplc.com</t>
         </is>
       </c>
-      <c r="P91" s="2" t="inlineStr">
+      <c r="Q91" s="2" t="inlineStr">
         <is>
           <t>Крупная tech-команда.</t>
         </is>
       </c>
-      <c r="Q91" s="2" t="inlineStr">
+      <c r="R91" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/www.asos.com?page=4</t>
         </is>
@@ -8072,29 +8528,29 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Единый центр возвратов маркетплейса с понятной маркировкой продавца на всех шагах.</t>
+          <t>Единый центр возвратов маркетплейса B&amp;Q: один вход, общий статус и правила для товаров B&amp;Q и сторонних продавцов.</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
+          <t>Понятная маркировка продавца на всех шагах (карточка, корзина, письмо) и правила ваучеров для товаров продавцов до оплаты.</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
           <t>N1, N3</t>
         </is>
       </c>
-      <c r="K92" s="5" t="inlineStr">
+      <c r="L92" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L92" s="2" t="inlineStr">
+      <c r="M92" s="2" t="inlineStr">
         <is>
           <t>CEO Thierry Garnier (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -8102,15 +8558,20 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
           <t>kingfisher.com</t>
         </is>
       </c>
-      <c r="P92" s="2" t="inlineStr">
+      <c r="Q92" s="2" t="inlineStr">
         <is>
           <t>Крупная компания.</t>
         </is>
       </c>
-      <c r="Q92" s="2" t="inlineStr">
+      <c r="R92" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/www.diy.com?page=8 ; https://kimola.com/reports/b-q-trustpilot-review-analysis-discover-customer-insights-trustpilot-en-gb-156279</t>
         </is>
@@ -8157,29 +8618,29 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-статус ремонта/рефанда + запись обратного звонка в слот.</t>
+          <t>Онлайн-статус ремонта и рефанда с этапами и сроками. Результат: меньше звонков и «обещали перезвонить».</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
+          <t>Запись обратного звонка в выбранный слот и решение вопросов онлайн для Ирландии вместо «езжайте в магазин».</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="K93" s="5" t="inlineStr">
+      <c r="L93" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L93" s="2" t="inlineStr">
+      <c r="M93" s="2" t="inlineStr">
         <is>
           <t>CEO Alex Baldock (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -8187,15 +8648,20 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
           <t>currysplc.com</t>
         </is>
       </c>
-      <c r="P93" s="2" t="inlineStr">
+      <c r="Q93" s="2" t="inlineStr">
         <is>
           <t>Крупная компания.</t>
         </is>
       </c>
-      <c r="Q93" s="2" t="inlineStr">
+      <c r="R93" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/www.currys.co.uk?page=9</t>
         </is>
@@ -8242,29 +8708,29 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Объяснение счёта и детектор аномалий + самозапись/отмена визита по счётчику.</t>
+          <t>«Объясни мой счёт» и детектор аномалий: расчётные счета при неисправном смарт-счётчике, резкие скачки.</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
+          <t>Самостоятельная запись, перенос и отмена визита по счётчику (без визитов без согласия) плюс исправление случайных разлогинов в приложении.</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
           <t>N6, N4</t>
         </is>
       </c>
-      <c r="K94" s="5" t="inlineStr">
+      <c r="L94" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L94" s="2" t="inlineStr">
+      <c r="M94" s="2" t="inlineStr">
         <is>
           <t>CEO Chris O'Shea (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -8272,15 +8738,20 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
           <t>centrica.com</t>
         </is>
       </c>
-      <c r="P94" s="2" t="inlineStr">
+      <c r="Q94" s="2" t="inlineStr">
         <is>
           <t>Крупная компания.</t>
         </is>
       </c>
-      <c r="Q94" s="2" t="inlineStr">
+      <c r="R94" s="2" t="inlineStr">
         <is>
           <t>https://citizensadvice.org.uk/scotland/consumer/your-energy/get-a-better-energy-deal/compare-domestic-energy-suppliers-customer-service/british-gas/details ; https://selectra.co.uk/energy/providers/british-gas/reviews</t>
         </is>
@@ -8327,29 +8798,29 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Мониторинг сбоев начисления бонусов + аудит онбординга app.</t>
+          <t>Аудит онбординга приложения: зависание на проверке телефона, вход, альтернативный способ подтверждения.</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
+          <t>Мониторинг начисления бонусов: сверка покупок на кассе и начислений, алерт при сбое и автоматическое доначисление.</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
           <t>N3, N2</t>
         </is>
       </c>
-      <c r="K95" s="5" t="inlineStr">
+      <c r="L95" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L95" s="2" t="inlineStr">
+      <c r="M95" s="2" t="inlineStr">
         <is>
           <t>CEO Roisin Currie (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -8357,15 +8828,20 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
           <t>corporate.greggs.co.uk</t>
         </is>
       </c>
-      <c r="P95" s="2" t="inlineStr">
+      <c r="Q95" s="2" t="inlineStr">
         <is>
           <t>Крупная компания.</t>
         </is>
       </c>
-      <c r="Q95" s="2" t="inlineStr">
+      <c r="R95" s="2" t="inlineStr">
         <is>
           <t>https://apps.apple.com/gb/app/greggs/id1098233626 ; https://unitq.com/unitq-scorecards/greggs</t>
         </is>
@@ -8412,29 +8888,29 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Перенос доставки в чат-боте + after-sales запись.</t>
+          <t>Перенос доставки прямо в чат-боте (сейчас бот не может это сделать) с выбором нового окна.</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
+          <t>After-sales запись на услугу (перевес двери, установка, вывоз старой техники) со статусом и ответственным.</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="K96" s="5" t="inlineStr">
+      <c r="L96" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L96" s="2" t="inlineStr">
+      <c r="M96" s="2" t="inlineStr">
         <is>
           <t>CEO John Roberts (основатель; по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -8442,15 +8918,20 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
           <t>ao-world.com</t>
         </is>
       </c>
-      <c r="P96" s="2" t="inlineStr">
+      <c r="Q96" s="2" t="inlineStr">
         <is>
           <t>Доказательства слабые.</t>
         </is>
       </c>
-      <c r="Q96" s="2" t="inlineStr">
+      <c r="R96" s="2" t="inlineStr">
         <is>
           <t>https://econsultancy.com/ao-trust-usp-customer-reviews-trustpilot/ ; https://ca.trustpilot.com/review/account.ao.com</t>
         </is>
@@ -8497,34 +8978,34 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Правила подбора сэмплов по профилю клиента + авто-обработка повреждений по фото.</t>
+          <t>Правила подбора сэмплов по профилю клиента (веган, аллергии), чтобы в заказ не попадало неподходящее.</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
+          <t>Автоматическая обработка повреждённых заказов по фото: замена за 24 часа без переписки.</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="K97" s="5" t="inlineStr">
+      <c r="L97" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L97" s="2" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>CEO Thomas Ryder (основатель; по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M97" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Customer.service@appliednutrition.uk (поддержка)</t>
         </is>
       </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -8532,10 +9013,15 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
           <t>Доказательства слабые.</t>
         </is>
       </c>
-      <c r="Q97" s="2" t="inlineStr">
+      <c r="R97" s="2" t="inlineStr">
         <is>
           <t>https://uk.trustpilot.com/review/appliednutrition.uk?page=9</t>
         </is>
@@ -8582,34 +9068,34 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Уведомления «снова в наличии» + прогноз задержек в праздники.</t>
+          <t>Уведомления «снова в наличии» и прогноз сроков отправки в праздники прямо в корзине.</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
+          <t>Мониторинг курьерских задержек (DPD) с проактивными письмами клиентам.</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="K98" s="5" t="inlineStr">
+      <c r="L98" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L98" s="2" t="inlineStr">
+      <c r="M98" s="2" t="inlineStr">
         <is>
           <t>CEO Sandy Chadha (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M98" s="2" t="inlineStr">
+      <c r="N98" s="2" t="inlineStr">
         <is>
           <t>contact@88vape.com (поддержка)</t>
         </is>
       </c>
-      <c r="N98" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -8617,10 +9103,15 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
           <t>Доказательства слабые.</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr">
+      <c r="R98" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/88vape.com?page=10</t>
         </is>
@@ -8667,29 +9158,29 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-запись вывоза с подтверждением и фото-подтверждением визита.</t>
+          <t>Онлайн-запись вывоза с подтверждением слота и фото-подтверждением визита. Результат: меньше споров «не приезжали, а счёт выставили».</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
+          <t>Self-service повторной записи и финального вывоза при закрытии офиса с прозрачной ценой.</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
           <t>N7</t>
         </is>
       </c>
-      <c r="K99" s="5" t="inlineStr">
+      <c r="L99" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L99" s="2" t="inlineStr">
+      <c r="M99" s="2" t="inlineStr">
         <is>
           <t>CEO Charles Skinner (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -8697,15 +9188,20 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
           <t>restoreplc.com</t>
         </is>
       </c>
-      <c r="P99" s="2" t="inlineStr">
+      <c r="Q99" s="2" t="inlineStr">
         <is>
           <t>Доказательства слабые.</t>
         </is>
       </c>
-      <c r="Q99" s="2" t="inlineStr">
+      <c r="R99" s="2" t="inlineStr">
         <is>
           <t>https://www.trustpilot.com/review/www.restore.co.uk</t>
         </is>
@@ -8752,29 +9248,29 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Инструменты для сообщества: публичный баг-трекер, сбор крэш-репортов, AI-кластеризация отзывов Steam.</t>
+          <t>AI-кластеризация отзывов Steam и сообщений форума: топ багов и запросов игроков после каждого патча.</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
+          <t>Публичный баг-трекер и сбор крэш-репортов для сообщества Planet Coaster 2 со статусами исправлений.</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="K100" s="5" t="inlineStr">
+      <c r="L100" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L100" s="2" t="inlineStr">
+      <c r="M100" s="2" t="inlineStr">
         <is>
           <t>CEO Jonny Watts (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -8782,15 +9278,20 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
           <t>frontier.co.uk</t>
         </is>
       </c>
-      <c r="P100" s="2" t="inlineStr">
+      <c r="Q100" s="2" t="inlineStr">
         <is>
           <t>Низкая применимость для новичка.</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr">
+      <c r="R100" s="2" t="inlineStr">
         <is>
           <t>https://vaporlens.app/app/2688950/planet_coaster_2 ; https://kotaku.com/planet-coaster-2-reviews-steam-worth-it-1851707808</t>
         </is>
@@ -8837,29 +9338,29 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-калькулятор оценки золота с прозрачной формулой + сбор отзывов.</t>
+          <t>Онлайн-калькулятор оценки золота с прозрачной формулой (вес, проба, цена дня). Результат: меньше подозрений в нечестной оценке.</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
+          <t>Автоматическая программа сбора отзывов после визита в ломбард и обмена валюты (сейчас клиентов не приглашают).</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
           <t>N3, N2</t>
         </is>
       </c>
-      <c r="K101" s="5" t="inlineStr">
+      <c r="L101" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L101" s="2" t="inlineStr">
+      <c r="M101" s="2" t="inlineStr">
         <is>
           <t>CEO Peter Kenyon; CFO Martin Clyburn</t>
         </is>
       </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -8867,22 +9368,27 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
           <t>+44 1642 579957</t>
         </is>
       </c>
-      <c r="P101" s="2" t="inlineStr">
+      <c r="Q101" s="2" t="inlineStr">
         <is>
           <t>Поглощение FirstCash (675p, ~£232m, закрытие 2П 2026) — может уже уйти с биржи.</t>
         </is>
       </c>
-      <c r="Q101" s="2" t="inlineStr">
+      <c r="R101" s="2" t="inlineStr">
         <is>
           <t>https://smartmoneypeople.com/ramsdens-reviews/products ; https://www.cityam.com/?p=2435877</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q101"/>
+  <autoFilter ref="A1:R101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9075,14 +9581,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9098,15 +9605,20 @@
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
-          <t>Что предложить</t>
+          <t>Предложение 1</t>
         </is>
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
+          <t>Предложение 2</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
           <t>Кому писать</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
@@ -9125,15 +9637,20 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Аудит и починка чекаута/платежей + AI-бот статуса заказа и предзаказа (автописьма о сроках, перенос/отмена в 1 клик).</t>
+          <t>Аудит и починка оплаты на hornby.com: найти, где и почему банк отклоняет карты, добавить Apple Pay и Google Pay, настроить алерты о сбоях оплаты. Результат: меньше брошенных корзин и жалоб «сайт не принимает оплату».</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>Трекер предзаказов: личная страница с ожидаемой датой, автописьма при переносе, кнопки «ждать», «заменить» или «вернуть деньги». Результат: предзаказы перестают отменяться молча через несколько месяцев.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>CEO Olly (Oliver) Raeburn; PR: Holly Barnett</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>— (в RNS email не указан)</t>
         </is>
@@ -9152,15 +9669,20 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Хелпдеск с AI-триажем писем + страница «где мой заказ» + автосообщения о задержках.</t>
+          <t>AI-триаж почты поддержки: входящие письма сортируются по темам (доставка, брак, возврат, подарочная карта), получают приоритет и готовый черновик ответа. Результат: ответ за часы, а не за дни.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Страница «Где мой заказ» с данными курьера и автоматическими письмами о задержке, плюс самостоятельная проверка баланса подарочной карты. Результат: меньше звонков и писем со статусом заказа.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>CEO Steven Crowe; CFO Sam Copeman</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>anglingdirect@fticonsulting.com (IR-агентство FTI)</t>
         </is>
@@ -9179,15 +9701,20 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Портал возвратов с фото-приёмкой + AI-ответы на письма с SLA + сбор отзывов после покупки.</t>
+          <t>Портал возвратов и брака: клиент загружает фото, система сразу решает по правилам (обмен, возврат или ваучер) и показывает статус. Результат: меньше споров и негативных отзывов про отказы.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Контроль обещания «ответ за 48 часов»: таймер на каждое письмо, эскалация при просрочке и AI-черновики ответов. Плюс автоматическая просьба оставить отзыв после покупки, чтобы поднять рейтинг reviews.io (сейчас 2.2).</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>CEO Anthony Smith (по RNS 2021 — проверить)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>— (в RNS скрыт)</t>
         </is>
@@ -9206,15 +9733,20 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Трекинг-страница + проактивные уведомления о задержках + AI-бот поддержки; модуль ответов на отзывы.</t>
+          <t>Проактивные уведомления о задержках: если посылка Evri застряла дольше X дней, клиент сам получает письмо или SMS с новым сроком и кнопкой «вернуть деньги». Результат: меньше заказов, которые «не пришли», и меньше злых отзывов.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>AI-ассистент поддержки на сайте и в почте плюс модуль ответов на отзывы в Trustpilot (сейчас компания не отвечает на негатив). Результат: рейтинг 2.0 начинает расти, обращения закрываются быстрее.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>CEO Gavin Peck</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>— (в RNS скрыт)</t>
         </is>
@@ -9233,15 +9765,20 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Прозрачный кабинет подписки: отмена/пауза в 2 клика, напоминания о списании (под требования DMCC Act).</t>
+          <t>Кабинет подписки Angel: отмена, пауза и изменение суммы в 2 клика, напоминание перед каждым списанием, честный экран удержания без dark patterns. Готовность к требованиям DMCC Act о подписках.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Автоматический возврат остатка баланса и удаление аккаунта по кнопке. Плюс мониторинг «списаний после отмены» с алертом. Результат: уходит главная причина негативных отзывов.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>CEO Rodrigo Maza; CFO Dominic Neary; IR Catherine Miles</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>IR@nakedwines.com</t>
         </is>
@@ -9260,15 +9797,20 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Единый трекер обращений (магазин+офис) + статус рефанда для клиента + AI-ответы на отзывы.</t>
+          <t>Единый трекер обращений для магазина, колл-центра и офиса: у клиента один номер обращения и онлайн-статус, клиента больше не перекидывают между отделами.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>Автоматический статус рефанда за возвраты и сэмплы плюс AI-черновики ответов на отзывы. Результат: отвечать на 100% негатива в течение суток вместо 64% за неделю.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>CEO Alex Jensen (назначен на смену Rob Parker — проверить); Co Sec Joanne Steer</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Joanne.steer@toppstiles.co.uk (Co Sec); toppstiles@citigatedewerogerson.com (IR-агентство)</t>
         </is>
@@ -9287,15 +9829,20 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Хелпдеск с SLA и AI-черновиками ответов + честный сбор отзывов после покупки.</t>
+          <t>Хелпдеск с SLA: у каждого письма таймер, AI-черновик и эскалация. Шаблонные ответы «передали в отдел» заменяются реальным решением.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Честная программа отзывов: автоматическая просьба об отзыве после доставки и отдельный путь для решения проблемы до публикации. Результат: reviews.io 1.7 начинает расти.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>CEO Lee Tappenden; CFO Dan Walden</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>investor.relations@procook.co.uk (IR); procook@mhpgroup.com (PR)</t>
         </is>
@@ -9314,15 +9861,20 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Лёгкий хелпдеск для онлайн-магазина + форма «бой/брак» с фото + проверка правил доставки в корзине.</t>
+          <t>Онлайн-форма «бой или брак» с фото и номером заказа, которая сразу отправляет в работу правильную замену (того же сервиза). Результат: заменяют то, что нужно, а не что-то другое.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>Проверка правил доставки в корзине (бесплатная доставка выше порога) и единый канал поддержки онлайн-заказов вместо «по телефону онлайн-заказами не занимаемся».</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>Group CEO Michael Scheepers (06/2026); FD Jonathan Hill</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>PortmeirionGroup@houston.co.uk (PR-агентство Houston)</t>
         </is>
@@ -9341,15 +9893,20 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-портал ремонта: заявка с фото, смета до отправки, статус и сроки; премиальный пост-покупочный сервис.</t>
+          <t>Онлайн-портал ремонта: заявка с фото, предварительная смета до отправки сумки, статус и срок ремонта. Результат: прозрачность вместо сюрприза «ремень за £240».</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>Премиальный пост-покупочный сервис: проверка подарочной записки и упаковки перед отправкой, персональный менеджер для повторных клиентов. Результат: защита люксового бренда в отзывах.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>CEO Andrea Baldo (проверить: смена директоров 08/2026)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>companysecretary@mulberry.com; mulberry@headlandconsultancy.com (PR)</t>
         </is>
@@ -9368,15 +9925,20 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Регистрация гарантии через QR на коробке за 30 секунд + онлайн-претензия с фото.</t>
+          <t>Регистрация гарантии через QR на коробке за 30 секунд, с напоминанием «зарегистрируйте до 30 дня». Результат: меньше отказов по гарантии и больше данных о покупателях.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Онлайн-претензия по гарантии с фото и видео, автоматическим решением и прямой доставкой замены, без отправки клиента обратно в магазин. Результат: меньше негатива к брендам Salter и Beldray.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>Новый CEO Simon Harrison (с 26.10.2026; Andrew Gossage ушёл)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>— (вопросы через investors.upplc.com)</t>
         </is>
@@ -9395,15 +9957,20 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-визуализатор/примерка обоев + отдельный модуль заказа и трекинга сэмплов.</t>
+          <t>Онлайн-визуализатор: клиент загружает фото комнаты и примеряет обои или ткань Morris &amp; Co. Результат: меньше ошибок с цветом и больше продаж.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>Отдельный модуль заказа сэмплов с трекингом каждого образца и понятной маркировкой, кто продавец (Morris &amp; Co или партнёр). Результат: уходят жалобы «оплатил 10 сэмплов, пришло 2».</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>CEO Lisa Montague; CFO Mike Woodcock</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>SDG@buchanan.uk.com (PR, 2024 — проверить)</t>
         </is>
@@ -9422,15 +9989,20 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Подтверждение надписи клиентом (превью) + единый трекер жалоб по 230+ франшизам с SLA.</t>
+          <t>Превью надписи на торте: клиент подтверждает текст и картинку перед изготовлением, а франшиза видит утверждённый макет. Результат: меньше ошибок в именах.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Центральный трекер жалоб для 230+ франшиз: SLA, статистика по магазинам, автоматическое решение (переделка или компенсация). Результат: проблемы не теряются на уровне отдельной точки.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>CEO Sukh Chamdal (основатель; по памяти — проверить)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>— (не найден в рамках лимита поиска)</t>
         </is>
@@ -9449,15 +10021,20 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PWA вместо отсутствующего Android-приложения + починка учёта членства и подарочных карт.</t>
+          <t>PWA (веб-приложение, которое ставится на телефон) для Android-пользователей и членов клуба: членские билеты, бронирование и подарочные карты без нативного приложения.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Починка учёта членства: корректная дата продления, баланс билетов, одинаковые комиссии в приложении и на сайте, приём e-подарочных карт онлайн. Результат: уходят главные жалобы с Trustpilot (2.5).</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>Interim CEO Farah Golant CBE (02/2026); FD Will Worsdell</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>everyman@almastrategic.com (PR, старый — проверить)</t>
         </is>
@@ -9476,15 +10053,20 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Онлайн-бронирование с апсейлами, депозитами и автонапоминаниями + CRM повторных визитов.</t>
+          <t>Новая воронка онлайн-бронирования: пакеты для групп, депозиты, апсейлы (еда, напитки, доп. игры), автонапоминания и снижение неявок. Результат: выручка с той же посещаемости.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>CRM повторных визитов: сбор контактов, акции на дни рождения и корпоративы, сегменты для рассылок. Результат: больше повторных посещений на слабом рынке.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>CEO Richard Harpham</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9503,15 +10085,20 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Мобильная версия бронирования/QR-заказа + система ответа на отзывы и жалобы.</t>
+          <t>Мобильная версия бронирования и QR-заказа: работает на любом телефоне и не запрашивает повторно данные, уже введённые для Wi-Fi.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Система приёма жалоб и ответов на отзывы по всем пабам: каждая жалоба уходит менеджеру паба с дедлайном. Результат: перестают теряться жалобы «3 раза писал — нет ответа».</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>CEO Justin Platt; Dir Corporate Affairs Giles Robinson</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>matthew.lee@marstons.co.uk (IR, 2025)</t>
         </is>
@@ -9530,15 +10117,20 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Новый B2B/B2C портал аренды: актуальное наличие, прозрачный калькулятор цены, письмо со сметой.</t>
+          <t>Новый портал аренды: актуальное наличие по депо, калькулятор цены со всеми сборами (доставка, вывоз) и письмо со сметой. Результат: портал перестаёт «падать 99% времени» и скрывать цены.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Мониторинг заказов: если деньги списаны, а заказ не создан, алерт и автоматический рефанд. Плюс автоматический расчёт дней аренды по фактическим датам доставки и вывоза.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>CEO Dan Evans (с 2022 — проверить 2026)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9557,15 +10149,20 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Трекер жалоб со статусом для клиента и SLA + ответы на отзывы.</t>
+          <t>Трекер жалоб с публичным статусом для клиента и SLA. Цель — закрывать жалобы быстрее нынешних 6+ недель.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Модуль ответов на отзывы Trustpilot с AI-черновиками (сейчас отвечают лишь на 63% негатива) и раздельная аналитика отзывов брокеров и инвесторов.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>CEO Rod Lockhart; IR Chris Semple</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>investorrelations@lendinvest.com (IR); complaints@lendinvest.com (жалобы)</t>
         </is>
@@ -9584,15 +10181,20 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Единый трекер ремонтов для всех франчайзи + сбор и ответы на отзывы по офисам.</t>
+          <t>Единый трекер ремонтов для всех франчайзи-офисов Belvoir: заявка с фото, подрядчик, SLA, статус для арендатора и арендодателя.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Модуль сбора и ответов на отзывы по каждому офису с рейтингом франчайзи. Результат: Trustpilot 2.5 растёт, а сеть видит проблемные офисы.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>CEO Gareth Samples</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>company.secretary@propertyfranchise.co.uk</t>
         </is>
@@ -9611,15 +10213,20 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Система ответов на отзывы для франчайзи + сбор отзывов после сделки.</t>
+          <t>Система ответов на отзывы для франчайзи: AI-черновики, единый стиль, SLA. Цель — отвечать на 100% негатива вместо 53–60%.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>Автоматический сбор отзывов после сделки или заселения плюс внутренний рейтинг офисов. Результат: защита бренда без попыток удалять отзывы.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>CEO Dominic Agace (по памяти — проверить)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>— (не найден в рамках лимита поиска)</t>
         </is>
@@ -9638,15 +10245,20 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Клиентский портал снаггинга: заявка с фото, слоты визита, статус, закрытие с подписью.</t>
+          <t>Клиентский портал снаггинга: дефект с фото, выбор слота визита, статус, закрытие с подписью покупателя.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>Аналитика повторяющихся дефектов по участкам и подрядчикам (окна, отопление, кровля) плюс публичные ответы на отзывы (сейчас их нет).</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>CEO Innes Smith</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9665,15 +10277,20 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Быстрый чекаут с Apple/Google Pay + проверка актуальности скидок партнёров.</t>
+          <t>Быстрый чекаут подарочных карт с Apple Pay и Google Pay в приложении Hapi. Результат: покупка за секунды вместо долгого оформления.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>Автоматическая проверка актуальности скидок партнёров (работает ли скидка в магазине, верен ли процент) с алертами. Результат: меньше жалоб на «обманные» скидки.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>CEO Paula Constant; CFO Matthew Cohen (06/2026)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>personalgroup@almastrategic.com (IR-агентство Alma)</t>
         </is>
